--- a/frontend/Frontend-Daily-Tracker.xlsx
+++ b/frontend/Frontend-Daily-Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\intern 2\Business-Listing\frontend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3DD8BA5-9D17-4C44-82E4-0A4A0523460C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A26BB3-2AA9-4B43-8A34-793FA553C6DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="80">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -67,9 +67,6 @@
     <t>Week 4</t>
   </si>
   <si>
-    <t>Remaining inner pages + finish the 3 required components</t>
-  </si>
-  <si>
     <t>Week 5</t>
   </si>
   <si>
@@ -254,6 +251,15 @@
   </si>
   <si>
     <t>Completed the Contact Form and started the Business Registration Process pages. Continued progressing through the inner-page development and established the initial structure for the registration flow.</t>
+  </si>
+  <si>
+    <t>Completed the remaining Business Registration Process pages and implemented the full registration flow across all stages. Added navigation restrictions so users cannot proceed to the next registration stage until the current stage has been completed, ensuring the required steps are followed in the correct order. Continued working on the Contact Form and started optimizing the newly developed pages and components. Also began researching suitable component libraries that could be used to improve the consistency, reusability, and development efficiency of the frontend.</t>
+  </si>
+  <si>
+    <t>feat: complete registration flow with step validation and optimize forms</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Completed the Business Registration Process and implemented sequential stage navigation to prevent users from skipping required steps. A total of 9 pages were developed, including the registration flow and Contact Form. Initial optimization work and component library research were also started</t>
   </si>
 </sst>
 </file>
@@ -362,7 +368,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -394,6 +400,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -740,7 +749,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -816,22 +825,22 @@
         <v>46259</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="2">
+        <v>8</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="2">
-        <v>8</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="198">
@@ -842,22 +851,22 @@
         <v>46260</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="F7" s="2">
+        <v>8</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="2">
-        <v>8</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="172.2">
@@ -868,22 +877,22 @@
         <v>46261</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="E8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="2">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="2">
-        <v>8</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="172.2">
@@ -894,22 +903,22 @@
         <v>46262</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="E9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="2">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="2">
-        <v>8</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="159">
@@ -920,22 +929,22 @@
         <v>46264</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="2">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="2">
-        <v>8</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="184.8">
@@ -949,19 +958,19 @@
         <v>12</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="2">
+        <v>8</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" s="2">
-        <v>8</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="184.8">
@@ -972,22 +981,22 @@
         <v>46266</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="2">
+        <v>8</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" s="2">
-        <v>8</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="H12" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="132">
@@ -998,22 +1007,22 @@
         <v>46267</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="2">
+        <v>8</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" s="2">
-        <v>8</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="118.8">
@@ -1024,22 +1033,22 @@
         <v>46268</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14" s="2">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" s="2">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="145.19999999999999">
@@ -1050,22 +1059,22 @@
         <v>46269</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="2">
+        <v>8</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F15" s="2">
-        <v>8</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="198">
@@ -1079,19 +1088,19 @@
         <v>13</v>
       </c>
       <c r="D16" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="2">
+        <v>8</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" s="2">
-        <v>8</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="H16" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="224.4">
@@ -1102,22 +1111,22 @@
         <v>46273</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D17" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" s="2">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F17" s="2">
-        <v>8</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="187.2">
@@ -1128,22 +1137,22 @@
         <v>46274</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" s="2">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F18" s="2">
-        <v>8</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="105.6">
@@ -1154,22 +1163,22 @@
         <v>46275</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" s="2">
+        <v>8</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F19" s="2">
-        <v>8</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="105.6">
@@ -1180,41 +1189,49 @@
         <v>46276</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" s="2">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F20" s="2">
-        <v>8</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="26.4">
+    </row>
+    <row r="21" spans="1:8" ht="158.4">
       <c r="A21" s="2">
         <v>16</v>
       </c>
-      <c r="B21" s="3"/>
+      <c r="B21" s="5">
+        <v>46279</v>
+      </c>
       <c r="C21" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
+        <v>29</v>
+      </c>
+      <c r="F21" s="2">
+        <v>8</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="2">
@@ -1278,10 +1295,10 @@
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>11</v>
@@ -1352,10 +1369,10 @@
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>11</v>
@@ -1426,10 +1443,10 @@
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>21</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>11</v>
@@ -1500,10 +1517,10 @@
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>11</v>

--- a/frontend/Frontend-Daily-Tracker.xlsx
+++ b/frontend/Frontend-Daily-Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\intern 2\Business-Listing\frontend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B9A32E9-6D36-4D3D-9E21-3D8BA61A5CC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{574BEE1A-2725-4DD7-B621-3FBA7F4B50AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="86">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -269,6 +269,15 @@
   </si>
   <si>
     <t>Improved the project architecture to support multiple business verticals through configurable data and reusable components. Added the Restaurant vertical and its related data while maintaining the existing Auto configuration. Continued optimization and researched component libraries for future frontend improvements</t>
+  </si>
+  <si>
+    <t>Completed the frontend development of the Chatbot, including the overall chatbot interface, layout, message display, input area, and user interaction elements. Integrated the chatbot into the existing website structure and refined its styling and responsiveness to maintain consistency with the rest of the frontend. Also continued improving the Listing Page by displaying business names instead of business IDs and fixed the Auto and Restaurant vertical toggle to ensure the correct website configuration and data are loaded when switching between the two versions.</t>
+  </si>
+  <si>
+    <t>feat: complete chatbot frontend and fix vertical switching</t>
+  </si>
+  <si>
+    <t>Completed the Chatbot frontend and integrated it into the existing project. Also fixed business name display on listings and refined the Auto and Restaurant vertical switching functionality</t>
   </si>
 </sst>
 </file>
@@ -406,12 +415,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -757,28 +766,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" ht="16.05" customHeight="1">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
     </row>
     <row r="4" spans="1:8" ht="22.05" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -1238,7 +1247,7 @@
       <c r="G21" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="H21" s="13" t="s">
+      <c r="H21" s="10" t="s">
         <v>79</v>
       </c>
     </row>
@@ -1268,19 +1277,31 @@
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" ht="158.4">
       <c r="A23" s="2">
         <v>18</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="3"/>
+      <c r="B23" s="5">
+        <v>46281</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>83</v>
+      </c>
       <c r="E23" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="2"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
+        <v>29</v>
+      </c>
+      <c r="F23" s="2">
+        <v>8</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="2">

--- a/frontend/Frontend-Daily-Tracker.xlsx
+++ b/frontend/Frontend-Daily-Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\intern 2\Business-Listing\frontend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{574BEE1A-2725-4DD7-B621-3FBA7F4B50AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1FB981B-2827-4FAB-8897-0FB4EEEB7B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="90">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -278,6 +278,18 @@
   </si>
   <si>
     <t>Completed the Chatbot frontend and integrated it into the existing project. Also fixed business name display on listings and refined the Auto and Restaurant vertical switching functionality</t>
+  </si>
+  <si>
+    <t>9/17/206</t>
+  </si>
+  <si>
+    <t>Improved the Chatbot functionality by making it listing-specific so that it can provide context related to individual business listings. Fixed issues with the brand name and ensured that the correct branding is displayed when switching between the Auto and Restaurant verticals. Implemented page transitions and scroll-based fade-in animations to improve the overall user experience. Added skeleton loading cards for smoother loading states and created hover effects for vehicle listings, including a hover line when users move over a car. Also implemented website transitions when users select or open a listing.</t>
+  </si>
+  <si>
+    <t>feat: improve chatbot, transitions, loading, and listing interactions</t>
+  </si>
+  <si>
+    <t>Improved the listing-specific chatbot, fixed branding issues between the Auto and Restaurant verticals, and added page transitions, scroll animations, skeleton cards, hover effects, and listing navigation transitions</t>
   </si>
 </sst>
 </file>
@@ -1303,19 +1315,31 @@
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" ht="158.4">
       <c r="A24" s="2">
         <v>19</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="3"/>
+      <c r="B24" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>87</v>
+      </c>
       <c r="E24" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="2"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
+        <v>29</v>
+      </c>
+      <c r="F24" s="2">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="2">

--- a/frontend/Frontend-Daily-Tracker.xlsx
+++ b/frontend/Frontend-Daily-Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\intern 2\Business-Listing\frontend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1FB981B-2827-4FAB-8897-0FB4EEEB7B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E10E413-D7ED-40D1-AB84-4C89397521C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="93">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -52,9 +52,6 @@
     <t>Week 1</t>
   </si>
   <si>
-    <t>Setup, TypeScript basics, sitemap + wireframe approval</t>
-  </si>
-  <si>
     <t>Todo</t>
   </si>
   <si>
@@ -290,6 +287,18 @@
   </si>
   <si>
     <t>Improved the listing-specific chatbot, fixed branding issues between the Auto and Restaurant verticals, and added page transitions, scroll animations, skeleton cards, hover effects, and listing navigation transitions</t>
+  </si>
+  <si>
+    <t>Initial Orientation, discussion about projects and the company, Group distributions.</t>
+  </si>
+  <si>
+    <t>Developed the Admin Dashboard and User Dashboard as part of the website’s dashboard and account management functionality. Implemented the layouts, navigation, content sections, and required interface elements while maintaining consistency with the existing frontend design. Made both dashboards fully responsive, adjusting and testing the layouts across desktop and mobile screen sizes. Continued implementing and refining the project’s interactive functionality, user flows, and frontend state handling. Reviewed existing components, fixed areas requiring improvement, and completed the remaining work planned for Week 6, including interaction, form-related, and state management functionality.Also reviewed the overall frontend structure to ensure the new dashboard components remained reusable and consistent with the Universal Business Listing Theme across different business types.</t>
+  </si>
+  <si>
+    <t>feat: add admin and user dashboards                 feat: complete week 6  validation, and state management</t>
+  </si>
+  <si>
+    <t>Completed the Admin and User Dashboards, optimized both for responsive layouts, and completed the planned Week 6 development work. Reviewed and refined the existing frontend functionality to ensure the new dashboard components integrate correctly with the rest of the project.</t>
   </si>
 </sst>
 </file>
@@ -779,7 +788,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -838,12 +847,14 @@
         <v>9</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="2"/>
+        <v>28</v>
+      </c>
+      <c r="F5" s="2">
+        <v>5</v>
+      </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
     </row>
@@ -855,22 +866,22 @@
         <v>46259</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="2">
+        <v>8</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="2">
-        <v>8</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="198">
@@ -881,22 +892,22 @@
         <v>46260</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="2">
+        <v>8</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="2">
-        <v>8</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="172.2">
@@ -907,22 +918,22 @@
         <v>46261</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="E8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="2">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="2">
-        <v>8</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="172.2">
@@ -933,22 +944,22 @@
         <v>46262</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="E9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="2">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="2">
-        <v>8</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="159">
@@ -959,22 +970,22 @@
         <v>46264</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="2">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="2">
-        <v>8</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="184.8">
@@ -985,22 +996,22 @@
         <v>46265</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="2">
+        <v>8</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" s="2">
-        <v>8</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="184.8">
@@ -1011,22 +1022,22 @@
         <v>46266</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="2">
+        <v>8</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F12" s="2">
-        <v>8</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="H12" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="132">
@@ -1037,22 +1048,22 @@
         <v>46267</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="2">
+        <v>8</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F13" s="2">
-        <v>8</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="118.8">
@@ -1063,22 +1074,22 @@
         <v>46268</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="2">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F14" s="2">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="145.19999999999999">
@@ -1089,22 +1100,22 @@
         <v>46269</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" s="2">
+        <v>8</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F15" s="2">
-        <v>8</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="198">
@@ -1115,22 +1126,22 @@
         <v>46272</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D16" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="2">
+        <v>8</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="2">
-        <v>8</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="H16" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="224.4">
@@ -1141,22 +1152,22 @@
         <v>46273</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D17" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" s="2">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F17" s="2">
-        <v>8</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="187.2">
@@ -1167,22 +1178,22 @@
         <v>46274</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="2">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F18" s="2">
-        <v>8</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="105.6">
@@ -1193,22 +1204,22 @@
         <v>46275</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F19" s="2">
+        <v>8</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F19" s="2">
-        <v>8</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="105.6">
@@ -1219,22 +1230,22 @@
         <v>46276</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" s="2">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F20" s="2">
-        <v>8</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="158.4">
@@ -1245,22 +1256,22 @@
         <v>46279</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D21" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" s="2">
+        <v>8</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F21" s="2">
-        <v>8</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="10" t="s">
         <v>78</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="224.4">
@@ -1271,22 +1282,22 @@
         <v>46280</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D22" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F22" s="2">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F22" s="2">
-        <v>8</v>
-      </c>
-      <c r="G22" s="3" t="s">
+      <c r="H22" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="158.4">
@@ -1297,22 +1308,22 @@
         <v>46281</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D23" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F23" s="2">
+        <v>8</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F23" s="2">
-        <v>8</v>
-      </c>
-      <c r="G23" s="3" t="s">
+      <c r="H23" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="158.4">
@@ -1320,40 +1331,52 @@
         <v>19</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F24" s="2">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F24" s="2">
-        <v>8</v>
-      </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
+    </row>
+    <row r="25" spans="1:8" ht="237.6">
       <c r="A25" s="2">
         <v>20</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="3"/>
+      <c r="B25" s="5">
+        <v>46283</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>90</v>
+      </c>
       <c r="E25" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="F25" s="2">
+        <v>8</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="2">
@@ -1361,13 +1384,13 @@
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="E26" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="3"/>
@@ -1381,7 +1404,7 @@
       <c r="C27" s="2"/>
       <c r="D27" s="3"/>
       <c r="E27" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="3"/>
@@ -1395,7 +1418,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="3"/>
       <c r="E28" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="3"/>
@@ -1409,7 +1432,7 @@
       <c r="C29" s="2"/>
       <c r="D29" s="3"/>
       <c r="E29" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="3"/>
@@ -1423,7 +1446,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="3"/>
       <c r="E30" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="3"/>
@@ -1435,13 +1458,13 @@
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="E31" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="3"/>
@@ -1455,7 +1478,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="3"/>
       <c r="E32" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="3"/>
@@ -1469,7 +1492,7 @@
       <c r="C33" s="2"/>
       <c r="D33" s="3"/>
       <c r="E33" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="3"/>
@@ -1483,7 +1506,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="3"/>
       <c r="E34" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="3"/>
@@ -1497,7 +1520,7 @@
       <c r="C35" s="2"/>
       <c r="D35" s="3"/>
       <c r="E35" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="3"/>
@@ -1509,13 +1532,13 @@
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="E36" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="3"/>
@@ -1529,7 +1552,7 @@
       <c r="C37" s="2"/>
       <c r="D37" s="3"/>
       <c r="E37" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="3"/>
@@ -1543,7 +1566,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="3"/>
       <c r="E38" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="3"/>
@@ -1557,7 +1580,7 @@
       <c r="C39" s="2"/>
       <c r="D39" s="3"/>
       <c r="E39" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="3"/>
@@ -1571,7 +1594,7 @@
       <c r="C40" s="2"/>
       <c r="D40" s="3"/>
       <c r="E40" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="3"/>
@@ -1583,13 +1606,13 @@
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="E41" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="3"/>
@@ -1603,7 +1626,7 @@
       <c r="C42" s="2"/>
       <c r="D42" s="3"/>
       <c r="E42" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="3"/>
@@ -1617,7 +1640,7 @@
       <c r="C43" s="2"/>
       <c r="D43" s="3"/>
       <c r="E43" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="3"/>
@@ -1631,7 +1654,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="3"/>
       <c r="E44" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="3"/>
@@ -1645,7 +1668,7 @@
       <c r="C45" s="2"/>
       <c r="D45" s="3"/>
       <c r="E45" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="3"/>

--- a/frontend/Frontend-Daily-Tracker.xlsx
+++ b/frontend/Frontend-Daily-Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\intern 2\Business-Listing\frontend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E10E413-D7ED-40D1-AB84-4C89397521C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC01442-17E1-4629-B36B-32982852DCAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="95">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -67,9 +67,6 @@
     <t>Week 5</t>
   </si>
   <si>
-    <t>Dashboard / modules (if applicable to this project)</t>
-  </si>
-  <si>
     <t>Week 6</t>
   </si>
   <si>
@@ -299,6 +296,15 @@
   </si>
   <si>
     <t>Completed the Admin and User Dashboards, optimized both for responsive layouts, and completed the planned Week 6 development work. Reviewed and refined the existing frontend functionality to ensure the new dashboard components integrate correctly with the rest of the project.</t>
+  </si>
+  <si>
+    <t>Integrated and expanded the frontend functionality across authentication, dashboards, bookings, listings, products, and administration. Added Forgot Password, Reset Password, social authentication callback, Privacy, Terms, Dashboard Bookings, and Admin Settings pages. Implemented reusable components for booking requests, business products, authentication, protected routes, listing forms, and image handling. Expanded the API integration to support password reset, contact forms, social login, product management, bookings, hero image management, image uploads, owner listings and accounts, and admin management of users and listings. Enhanced the Owner Dashboard with product management, image uploads, account editing, and booking management, while updating the Admin section with functionality for users, listings, and hero images. The newly implemented features are integrated into the frontend and use demo data where the required backend functionality or data is not yet available, allowing the features to be developed and tested while the backend catches up. Also updated the project types, authentication handling, booking and review functionality, listing forms, and theme configuration.</t>
+  </si>
+  <si>
+    <t>feat: expand auth, dashboards, bookings, products, and backend integration</t>
+  </si>
+  <si>
+    <t>New frontend features and backend integrations have been implemented and connected to the project. Demo data is currently used for functionality where the corresponding backend endpoints or data are not yet available, with the structure prepared for integration once the backend implementation is completed.</t>
   </si>
 </sst>
 </file>
@@ -788,7 +794,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -847,10 +853,10 @@
         <v>9</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F5" s="2">
         <v>5</v>
@@ -866,22 +872,22 @@
         <v>46259</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="2">
+        <v>8</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="2">
-        <v>8</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="198">
@@ -892,22 +898,22 @@
         <v>46260</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="2">
+        <v>8</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="2">
-        <v>8</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="172.2">
@@ -918,22 +924,22 @@
         <v>46261</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="E8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="2">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="2">
-        <v>8</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="172.2">
@@ -944,22 +950,22 @@
         <v>46262</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="E9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="2">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="2">
-        <v>8</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="159">
@@ -970,22 +976,22 @@
         <v>46264</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="2">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F10" s="2">
-        <v>8</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="184.8">
@@ -999,19 +1005,19 @@
         <v>11</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="2">
+        <v>8</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" s="2">
-        <v>8</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="184.8">
@@ -1022,22 +1028,22 @@
         <v>46266</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="2">
+        <v>8</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F12" s="2">
-        <v>8</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="H12" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="132">
@@ -1048,22 +1054,22 @@
         <v>46267</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="2">
+        <v>8</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13" s="2">
-        <v>8</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="118.8">
@@ -1074,22 +1080,22 @@
         <v>46268</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="2">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14" s="2">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="145.19999999999999">
@@ -1100,22 +1106,22 @@
         <v>46269</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="2">
+        <v>8</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" s="2">
-        <v>8</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="198">
@@ -1129,19 +1135,19 @@
         <v>12</v>
       </c>
       <c r="D16" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="2">
+        <v>8</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="2">
-        <v>8</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="H16" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="224.4">
@@ -1152,22 +1158,22 @@
         <v>46273</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D17" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="2">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17" s="2">
-        <v>8</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="187.2">
@@ -1178,22 +1184,22 @@
         <v>46274</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D18" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="2">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" s="2">
-        <v>8</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="105.6">
@@ -1204,22 +1210,22 @@
         <v>46275</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" s="2">
+        <v>8</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F19" s="2">
-        <v>8</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="105.6">
@@ -1230,22 +1236,22 @@
         <v>46276</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="2">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" s="2">
-        <v>8</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="158.4">
@@ -1259,19 +1265,19 @@
         <v>13</v>
       </c>
       <c r="D21" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" s="2">
+        <v>8</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F21" s="2">
-        <v>8</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="224.4">
@@ -1282,22 +1288,22 @@
         <v>46280</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D22" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" s="2">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F22" s="2">
-        <v>8</v>
-      </c>
-      <c r="G22" s="3" t="s">
+      <c r="H22" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="158.4">
@@ -1308,22 +1314,22 @@
         <v>46281</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D23" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="2">
+        <v>8</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F23" s="2">
-        <v>8</v>
-      </c>
-      <c r="G23" s="3" t="s">
+      <c r="H23" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="158.4">
@@ -1331,25 +1337,25 @@
         <v>19</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" s="2">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F24" s="2">
-        <v>8</v>
-      </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="237.6">
@@ -1360,41 +1366,49 @@
         <v>46283</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D25" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" s="2">
+        <v>8</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F25" s="2">
-        <v>8</v>
-      </c>
-      <c r="G25" s="3" t="s">
+      <c r="H25" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
+    </row>
+    <row r="26" spans="1:8" ht="316.8">
       <c r="A26" s="2">
         <v>21</v>
       </c>
-      <c r="B26" s="3"/>
+      <c r="B26" s="5">
+        <v>46286</v>
+      </c>
       <c r="C26" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" s="2"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
+        <v>27</v>
+      </c>
+      <c r="F26" s="2">
+        <v>8</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="2">
@@ -1458,10 +1472,10 @@
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>10</v>
@@ -1532,10 +1546,10 @@
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>10</v>
@@ -1606,10 +1620,10 @@
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>21</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>10</v>

--- a/frontend/Frontend-Daily-Tracker.xlsx
+++ b/frontend/Frontend-Daily-Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\intern 2\Business-Listing\frontend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC01442-17E1-4629-B36B-32982852DCAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E10E413-D7ED-40D1-AB84-4C89397521C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="93">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -67,6 +67,9 @@
     <t>Week 5</t>
   </si>
   <si>
+    <t>Dashboard / modules (if applicable to this project)</t>
+  </si>
+  <si>
     <t>Week 6</t>
   </si>
   <si>
@@ -296,15 +299,6 @@
   </si>
   <si>
     <t>Completed the Admin and User Dashboards, optimized both for responsive layouts, and completed the planned Week 6 development work. Reviewed and refined the existing frontend functionality to ensure the new dashboard components integrate correctly with the rest of the project.</t>
-  </si>
-  <si>
-    <t>Integrated and expanded the frontend functionality across authentication, dashboards, bookings, listings, products, and administration. Added Forgot Password, Reset Password, social authentication callback, Privacy, Terms, Dashboard Bookings, and Admin Settings pages. Implemented reusable components for booking requests, business products, authentication, protected routes, listing forms, and image handling. Expanded the API integration to support password reset, contact forms, social login, product management, bookings, hero image management, image uploads, owner listings and accounts, and admin management of users and listings. Enhanced the Owner Dashboard with product management, image uploads, account editing, and booking management, while updating the Admin section with functionality for users, listings, and hero images. The newly implemented features are integrated into the frontend and use demo data where the required backend functionality or data is not yet available, allowing the features to be developed and tested while the backend catches up. Also updated the project types, authentication handling, booking and review functionality, listing forms, and theme configuration.</t>
-  </si>
-  <si>
-    <t>feat: expand auth, dashboards, bookings, products, and backend integration</t>
-  </si>
-  <si>
-    <t>New frontend features and backend integrations have been implemented and connected to the project. Demo data is currently used for functionality where the corresponding backend endpoints or data are not yet available, with the structure prepared for integration once the backend implementation is completed.</t>
   </si>
 </sst>
 </file>
@@ -794,7 +788,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -853,10 +847,10 @@
         <v>9</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F5" s="2">
         <v>5</v>
@@ -872,22 +866,22 @@
         <v>46259</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6" s="2">
         <v>8</v>
       </c>
       <c r="G6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="198">
@@ -898,22 +892,22 @@
         <v>46260</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F7" s="2">
         <v>8</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="172.2">
@@ -924,22 +918,22 @@
         <v>46261</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8" s="2">
         <v>8</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="172.2">
@@ -950,22 +944,22 @@
         <v>46262</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F9" s="2">
         <v>8</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="159">
@@ -976,22 +970,22 @@
         <v>46264</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="2">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="2">
-        <v>8</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="184.8">
@@ -1005,19 +999,19 @@
         <v>11</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F11" s="2">
         <v>8</v>
       </c>
       <c r="G11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="184.8">
@@ -1028,22 +1022,22 @@
         <v>46266</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F12" s="2">
         <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="132">
@@ -1054,22 +1048,22 @@
         <v>46267</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F13" s="2">
         <v>8</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="118.8">
@@ -1080,22 +1074,22 @@
         <v>46268</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F14" s="2">
         <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="145.19999999999999">
@@ -1106,22 +1100,22 @@
         <v>46269</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F15" s="2">
         <v>8</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="198">
@@ -1135,19 +1129,19 @@
         <v>12</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F16" s="2">
         <v>8</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="224.4">
@@ -1158,22 +1152,22 @@
         <v>46273</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F17" s="2">
         <v>8</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="187.2">
@@ -1184,22 +1178,22 @@
         <v>46274</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F18" s="2">
         <v>8</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="105.6">
@@ -1210,22 +1204,22 @@
         <v>46275</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F19" s="2">
         <v>8</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="105.6">
@@ -1236,22 +1230,22 @@
         <v>46276</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F20" s="2">
         <v>8</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="158.4">
@@ -1265,19 +1259,19 @@
         <v>13</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F21" s="2">
         <v>8</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="224.4">
@@ -1288,22 +1282,22 @@
         <v>46280</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F22" s="2">
         <v>8</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="158.4">
@@ -1314,22 +1308,22 @@
         <v>46281</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F23" s="2">
         <v>8</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="158.4">
@@ -1337,25 +1331,25 @@
         <v>19</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F24" s="2">
         <v>8</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="237.6">
@@ -1366,49 +1360,41 @@
         <v>46283</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F25" s="2">
         <v>8</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="316.8">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="2">
         <v>21</v>
       </c>
-      <c r="B26" s="5">
-        <v>46286</v>
-      </c>
+      <c r="B26" s="3"/>
       <c r="C26" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F26" s="2">
-        <v>8</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>94</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F26" s="2"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="2">
@@ -1472,10 +1458,10 @@
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>10</v>
@@ -1546,10 +1532,10 @@
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>10</v>
@@ -1620,10 +1606,10 @@
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>10</v>

--- a/frontend/Frontend-Daily-Tracker.xlsx
+++ b/frontend/Frontend-Daily-Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\intern 2\Business-Listing\frontend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E10E413-D7ED-40D1-AB84-4C89397521C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1372D24F-AA6D-4243-A552-E84589D457A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="99">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -67,9 +67,6 @@
     <t>Week 5</t>
   </si>
   <si>
-    <t>Dashboard / modules (if applicable to this project)</t>
-  </si>
-  <si>
     <t>Week 6</t>
   </si>
   <si>
@@ -299,6 +296,62 @@
   </si>
   <si>
     <t>Completed the Admin and User Dashboards, optimized both for responsive layouts, and completed the planned Week 6 development work. Reviewed and refined the existing frontend functionality to ensure the new dashboard components integrate correctly with the rest of the project.</t>
+  </si>
+  <si>
+    <t>9/212026</t>
+  </si>
+  <si>
+    <t>Integrated and expanded the frontend functionality
+across authentication, dashboards, bookings, listings
+products, and administration. Added Forgot
+Password, Reset Password, social authentication
+callback, Privacy, Terms, Dashboard Bookings, and
+Admin Settings pages. Implemented reusable
+components for booking requests, business products,
+authentication, protected routes, listing forms, and
+image handling. Expanded the API integration to
+support password reset, contact forms, social login,
+product management, bookings, hero image
+management, image uploads, owner listings and
+accounts, and admin management of users and
+listings. Enhanced the Owner Dashboard with
+product management, image uploads, account
+editing, and booking management, while updating the
+Admin section with functionality for users, listings,
+and hero images. The newly implemented features
+are integrated into the frontend and use demo data
+where the required backend functionality or data is
+not yet available, allowing the features to be
+developed and tested while the backend catches up.
+Also updated the project types, authentication
+handling, booking and review functionality, listing
+forms, and theme configuration.</t>
+  </si>
+  <si>
+    <t>feat: expand auth,
+dashboards, bookings,
+products, and backend
+integration</t>
+  </si>
+  <si>
+    <t>New frontend features and backend
+integrations have been implemented
+and connected to the project. Demo
+data is currently used for functionality
+where the corresponding backend
+endpoints or data are not yet available,
+with the structure prepared for
+integration once the backend
+implementation is completed.</t>
+  </si>
+  <si>
+    <t>Improved the frontend by making it capable of handling REST API backend data and expanded the way listing information is processed and displayed. Improved location handling by adding address geocoding for listings without coordinates and updated distance sorting to correctly handle listings without available distance data. Updated business listings and registration forms to support website and social media information including Facebook, Instagram, TikTok, and LinkedIn. Added live listing counts to the Homepage category showcase. Continued optimizing image handling by using Next.js Image components across key pages and components. Improved the registration page's mobile layout with a compact step indicator and added vertical-specific logos for the Auto and Restaurant versions. Also added and refined site metadata, canonical URLs, robots settings, sitemap, Open Graph information, and other SEO-related configurations.</t>
+  </si>
+  <si>
+    <t>feat: enhance API data, listings, forms, SEO, images, and responsive UI</t>
+  </si>
+  <si>
+    <t>No blockers. Improved REST API data handling, listing and location processing, image optimization, responsive layouts, social information support, and SEO configuration across the frontend.</t>
   </si>
 </sst>
 </file>
@@ -788,7 +841,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -847,10 +900,10 @@
         <v>9</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F5" s="2">
         <v>5</v>
@@ -866,22 +919,22 @@
         <v>46259</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="2">
+        <v>8</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="2">
-        <v>8</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="198">
@@ -892,22 +945,22 @@
         <v>46260</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="2">
+        <v>8</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="2">
-        <v>8</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="172.2">
@@ -918,22 +971,22 @@
         <v>46261</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="E8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="2">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="2">
-        <v>8</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="172.2">
@@ -944,22 +997,22 @@
         <v>46262</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="E9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="2">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="2">
-        <v>8</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="159">
@@ -970,22 +1023,22 @@
         <v>46264</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="2">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F10" s="2">
-        <v>8</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="184.8">
@@ -999,19 +1052,19 @@
         <v>11</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="2">
+        <v>8</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" s="2">
-        <v>8</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="184.8">
@@ -1022,22 +1075,22 @@
         <v>46266</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="2">
+        <v>8</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F12" s="2">
-        <v>8</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="H12" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="132">
@@ -1048,22 +1101,22 @@
         <v>46267</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="2">
+        <v>8</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13" s="2">
-        <v>8</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="118.8">
@@ -1074,22 +1127,22 @@
         <v>46268</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="2">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14" s="2">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="145.19999999999999">
@@ -1100,22 +1153,22 @@
         <v>46269</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="2">
+        <v>8</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" s="2">
-        <v>8</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="198">
@@ -1129,19 +1182,19 @@
         <v>12</v>
       </c>
       <c r="D16" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="2">
+        <v>8</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="2">
-        <v>8</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="H16" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="224.4">
@@ -1152,22 +1205,22 @@
         <v>46273</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D17" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="2">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17" s="2">
-        <v>8</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="187.2">
@@ -1178,22 +1231,22 @@
         <v>46274</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D18" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="2">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" s="2">
-        <v>8</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="105.6">
@@ -1204,22 +1257,22 @@
         <v>46275</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" s="2">
+        <v>8</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F19" s="2">
-        <v>8</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="105.6">
@@ -1230,22 +1283,22 @@
         <v>46276</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="2">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" s="2">
-        <v>8</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="158.4">
@@ -1259,19 +1312,19 @@
         <v>13</v>
       </c>
       <c r="D21" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" s="2">
+        <v>8</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F21" s="2">
-        <v>8</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="224.4">
@@ -1282,22 +1335,22 @@
         <v>46280</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D22" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" s="2">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F22" s="2">
-        <v>8</v>
-      </c>
-      <c r="G22" s="3" t="s">
+      <c r="H22" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="158.4">
@@ -1308,22 +1361,22 @@
         <v>46281</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D23" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="2">
+        <v>8</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F23" s="2">
-        <v>8</v>
-      </c>
-      <c r="G23" s="3" t="s">
+      <c r="H23" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="158.4">
@@ -1331,25 +1384,25 @@
         <v>19</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" s="2">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F24" s="2">
-        <v>8</v>
-      </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="237.6">
@@ -1360,55 +1413,75 @@
         <v>46283</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D25" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" s="2">
+        <v>8</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F25" s="2">
-        <v>8</v>
-      </c>
-      <c r="G25" s="3" t="s">
+      <c r="H25" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
+    </row>
+    <row r="26" spans="1:8" ht="330">
       <c r="A26" s="2">
         <v>21</v>
       </c>
-      <c r="B26" s="3"/>
+      <c r="B26" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="C26" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>15</v>
+        <v>93</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" s="2"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-    </row>
-    <row r="27" spans="1:8">
+        <v>27</v>
+      </c>
+      <c r="F26" s="2">
+        <v>8</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="250.8">
       <c r="A27" s="2">
         <v>22</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="3"/>
+      <c r="B27" s="5">
+        <v>46287</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>96</v>
+      </c>
       <c r="E27" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" s="2"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
+        <v>27</v>
+      </c>
+      <c r="F27" s="2">
+        <v>8</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="2">
@@ -1458,10 +1531,10 @@
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>10</v>
@@ -1532,10 +1605,10 @@
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>10</v>
@@ -1606,10 +1679,10 @@
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>21</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>10</v>

--- a/frontend/Frontend-Daily-Tracker.xlsx
+++ b/frontend/Frontend-Daily-Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\intern 2\Business-Listing\frontend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1372D24F-AA6D-4243-A552-E84589D457A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEA30940-65DD-495B-BE6B-292170D28005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="102">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -352,6 +352,15 @@
   </si>
   <si>
     <t>No blockers. Improved REST API data handling, listing and location processing, image optimization, responsive layouts, social information support, and SEO configuration across the frontend.</t>
+  </si>
+  <si>
+    <t>Expanded the Admin Dashboard with category management, allowing administrators to create, edit, and delete categories and manage category icons. Added user management functionality for banning and unbanning users, including confirmation handling and status indicators, and added an admin broadcast feature for sending announcements. Added customer activity management to the Owner Dashboard, allowing business owners to view customers along with their bookings, reviews, and chat activity, and added customer messaging and announcement functionality. Added a dedicated customer activity page for individual business listings within the Admin Dashboard. Improved the registration and listing forms to use live category data and expanded category handling throughout the frontend. Added customer-related API integration, including customer activity, announcements, bookings, reviews, and messaging data. Also continued improving image handling with Next.js Image components, added category icons, improved error handling, and refined the frontend pages and dashboard interactions.</t>
+  </si>
+  <si>
+    <t>feat: add customer management, category controls, and admin features</t>
+  </si>
+  <si>
+    <t>No blockers. Expanded the Admin and Owner Dashboard functionality with category management, user controls, customer activity, announcements, and additional business management features. Integrated the new functionality with the available API endpoints while keeping demo data where backend functionality is not yet available. Continued improving image handling, error states, category handling, and overall frontend structure.</t>
   </si>
 </sst>
 </file>
@@ -460,7 +469,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -495,6 +504,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -911,7 +923,7 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="1:8" ht="171.6">
+    <row r="6" spans="1:8" ht="184.8">
       <c r="A6" s="2">
         <v>1</v>
       </c>
@@ -1145,7 +1157,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="145.19999999999999">
+    <row r="15" spans="1:8" ht="158.4">
       <c r="A15" s="2">
         <v>10</v>
       </c>
@@ -1457,7 +1469,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="250.8">
+    <row r="27" spans="1:8" ht="264">
       <c r="A27" s="2">
         <v>22</v>
       </c>
@@ -1483,19 +1495,31 @@
         <v>98</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" ht="290.39999999999998">
       <c r="A28" s="2">
         <v>23</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="3"/>
+      <c r="B28" s="5">
+        <v>46288</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>99</v>
+      </c>
       <c r="E28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" s="2"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
+        <v>27</v>
+      </c>
+      <c r="F28" s="2">
+        <v>8</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="2">

--- a/frontend/Frontend-Daily-Tracker.xlsx
+++ b/frontend/Frontend-Daily-Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\intern 2\Business-Listing\frontend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE31BD1-8D20-40F9-AB27-E5E171220D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D2C35C9-4AF4-4A57-9466-4BD3E54206EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="110">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -68,9 +68,6 @@
   </si>
   <si>
     <t>Week 6</t>
-  </si>
-  <si>
-    <t>Interactivity, form validation, state management</t>
   </si>
   <si>
     <t>Week 7</t>
@@ -379,6 +376,15 @@
   </si>
   <si>
     <t>No blockers. Backend integration is currently in full swing, with ongoing coordination with the backend developer to connect and align frontend functionality with the available APIs. Continued development of the AI Chatbot integration and improved the Listing Map by adding custom business-name markers and direct navigation to individual listings</t>
+  </si>
+  <si>
+    <t>Continued frontend development and integration with the backend, with the AI and Chatbot functionality being further integrated into the website. Improved the listing-specific Chatbot and chat management flow, including chat sessions, messages, owner/admin chat inboxes, and conversation handling. Continued improving the Listing Map functionality with custom business-name markers and direct interaction with listings. Refined the frontend’s REST API integration and data handling to support the growing backend functionality. Continued improving the Auto and Restaurant vertical configurations and ensuring the correct data, branding, and content are displayed based on the selected vertical. Also worked on customer, booking, product, listing, and dashboard-related functionality as part of the ongoing backend integration. Had discussions with the backend developer regarding the current integration progress, API requirements, and the next steps for connecting the remaining frontend functionality.</t>
+  </si>
+  <si>
+    <t>feat: complete frontend integration with backend and AI services</t>
+  </si>
+  <si>
+    <t>Frontend and backend integration is in full swing, with continued work on the AI Chatbot, REST API integration, listing functionality, maps, dashboards, and vertical-specific data. Coordinated with the backend developer to align the frontend implementation with the available APIs and ongoing backend development</t>
   </si>
 </sst>
 </file>
@@ -868,7 +874,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -927,10 +933,10 @@
         <v>9</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F5" s="2">
         <v>5</v>
@@ -946,22 +952,22 @@
         <v>46259</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="2">
+        <v>8</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="2">
-        <v>8</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="198">
@@ -972,22 +978,22 @@
         <v>46260</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="2">
+        <v>8</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="2">
-        <v>8</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="172.2">
@@ -998,22 +1004,22 @@
         <v>46261</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="E8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="2">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="2">
-        <v>8</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="172.2">
@@ -1024,22 +1030,22 @@
         <v>46262</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="E9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="2">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="2">
-        <v>8</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="159">
@@ -1050,22 +1056,22 @@
         <v>46264</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="2">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="2">
-        <v>8</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="184.8">
@@ -1079,19 +1085,19 @@
         <v>11</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="2">
+        <v>8</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="2">
-        <v>8</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="184.8">
@@ -1102,22 +1108,22 @@
         <v>46266</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="2">
+        <v>8</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="2">
-        <v>8</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="H12" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="132">
@@ -1128,22 +1134,22 @@
         <v>46267</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="2">
+        <v>8</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" s="2">
-        <v>8</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="118.8">
@@ -1154,22 +1160,22 @@
         <v>46268</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="2">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="2">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="145.19999999999999">
@@ -1180,22 +1186,22 @@
         <v>46269</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="2">
+        <v>8</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" s="2">
-        <v>8</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="198">
@@ -1209,19 +1215,19 @@
         <v>12</v>
       </c>
       <c r="D16" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="2">
+        <v>8</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" s="2">
-        <v>8</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="H16" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="224.4">
@@ -1232,22 +1238,22 @@
         <v>46273</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D17" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="2">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" s="2">
-        <v>8</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="187.2">
@@ -1258,22 +1264,22 @@
         <v>46274</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D18" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" s="2">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F18" s="2">
-        <v>8</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="105.6">
@@ -1284,22 +1290,22 @@
         <v>46275</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" s="2">
+        <v>8</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F19" s="2">
-        <v>8</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="105.6">
@@ -1310,22 +1316,22 @@
         <v>46276</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" s="2">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F20" s="2">
-        <v>8</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="158.4">
@@ -1339,19 +1345,19 @@
         <v>13</v>
       </c>
       <c r="D21" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" s="2">
+        <v>8</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F21" s="2">
-        <v>8</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="10" t="s">
         <v>76</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="224.4">
@@ -1362,22 +1368,22 @@
         <v>46280</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D22" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="2">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F22" s="2">
-        <v>8</v>
-      </c>
-      <c r="G22" s="3" t="s">
+      <c r="H22" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="158.4">
@@ -1388,22 +1394,22 @@
         <v>46281</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D23" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="2">
+        <v>8</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F23" s="2">
-        <v>8</v>
-      </c>
-      <c r="G23" s="3" t="s">
+      <c r="H23" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="158.4">
@@ -1411,25 +1417,25 @@
         <v>19</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" s="2">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F24" s="2">
-        <v>8</v>
-      </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="237.6">
@@ -1440,22 +1446,22 @@
         <v>46283</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D25" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="2">
+        <v>8</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F25" s="2">
-        <v>8</v>
-      </c>
-      <c r="G25" s="3" t="s">
+      <c r="H25" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="330">
@@ -1463,25 +1469,25 @@
         <v>21</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D26" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F26" s="2">
+        <v>8</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F26" s="2">
-        <v>8</v>
-      </c>
-      <c r="G26" s="3" t="s">
+      <c r="H26" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="250.8">
@@ -1492,22 +1498,22 @@
         <v>46287</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D27" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" s="2">
+        <v>8</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F27" s="2">
-        <v>8</v>
-      </c>
-      <c r="G27" s="3" t="s">
+      <c r="H27" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="290.39999999999998">
@@ -1518,22 +1524,22 @@
         <v>46288</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D28" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F28" s="2">
+        <v>8</v>
+      </c>
+      <c r="G28" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F28" s="2">
-        <v>8</v>
-      </c>
-      <c r="G28" s="3" t="s">
+      <c r="H28" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="316.8">
@@ -1544,22 +1550,22 @@
         <v>46289</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D29" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F29" s="2">
+        <v>8</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F29" s="2">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
+      <c r="H29" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="238.2">
@@ -1570,41 +1576,49 @@
         <v>46290</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D30" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F30" s="2">
+        <v>8</v>
+      </c>
+      <c r="G30" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F30" s="2">
-        <v>8</v>
-      </c>
-      <c r="G30" s="3" t="s">
+      <c r="H30" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="H30" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
+    </row>
+    <row r="31" spans="1:8" ht="264">
       <c r="A31" s="2">
         <v>26</v>
       </c>
-      <c r="B31" s="3"/>
+      <c r="B31" s="5">
+        <v>46293</v>
+      </c>
       <c r="C31" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>16</v>
+        <v>107</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" s="2"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
+        <v>26</v>
+      </c>
+      <c r="F31" s="2">
+        <v>8</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="2">
@@ -1668,10 +1682,10 @@
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>10</v>
@@ -1742,10 +1756,10 @@
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>20</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>10</v>

--- a/frontend/Frontend-Daily-Tracker.xlsx
+++ b/frontend/Frontend-Daily-Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\intern 2\Business-Listing\frontend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D2C35C9-4AF4-4A57-9466-4BD3E54206EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8AB4A80-D203-431A-BD82-96CA2D9D5D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="113">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -385,6 +385,15 @@
   </si>
   <si>
     <t>Frontend and backend integration is in full swing, with continued work on the AI Chatbot, REST API integration, listing functionality, maps, dashboards, and vertical-specific data. Coordinated with the backend developer to align the frontend implementation with the available APIs and ongoing backend development</t>
+  </si>
+  <si>
+    <t>Continued improving and restructuring the frontend as part of the complete integration phase. Refactored the Admin Dashboard into separate reusable pages and components for Overview, Categories, Listings, Reviews, Settings, and Users, while improving the related admin functionality and shared structures. Added a frontend testing setup using Vitest and introduced tests for booking functionality, social authentication, integration configuration, site configuration, theme configuration, and form and interaction validation. Updated and refined major frontend components and sections including authentication, listings, maps, bookings, reviews, registration, chatbot, dashboard, customer management, and homepage functionality. Also improved the project configuration, API service layer, validation utilities, error handling, and overall frontend structure while continuing the integration with the backend.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> git commit -m "feat: new admin files, add testing, improve integrations, and update frontend features"</t>
+  </si>
+  <si>
+    <t>Completed  frontend restructuring and added automated tests for key frontend functionality and configuration. Refactored the Admin Dashboard into separate maintainable sections and continued refining the integrated authentication, listings, bookings, chatbot, customer, map, and dashboard features</t>
   </si>
 </sst>
 </file>
@@ -1620,19 +1629,31 @@
         <v>109</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" ht="250.8">
       <c r="A32" s="2">
         <v>27</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="3"/>
+      <c r="B32" s="5">
+        <v>46294</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="E32" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" s="2"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
+        <v>26</v>
+      </c>
+      <c r="F32" s="2">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="2">

--- a/frontend/Frontend-Daily-Tracker.xlsx
+++ b/frontend/Frontend-Daily-Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\intern 2\Business-Listing\frontend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8AB4A80-D203-431A-BD82-96CA2D9D5D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C098D1ED-FB8F-47C6-8CD0-395AF320E0CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="115">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -394,6 +394,12 @@
   </si>
   <si>
     <t>Completed  frontend restructuring and added automated tests for key frontend functionality and configuration. Refactored the Admin Dashboard into separate maintainable sections and continued refining the integrated authentication, listings, bookings, chatbot, customer, map, and dashboard features</t>
+  </si>
+  <si>
+    <t>Participated in two meetings and discussions regarding the transition to the upcoming SaaS project and the remaining work for the current project. Reviewed the current project to identify and audit the implemented features, discussed the completion of all remaining elements, and planned the next steps for moving into the SaaS development phase. Also initiated the process of transferring and working with real data as part of the transition from the current development setup</t>
+  </si>
+  <si>
+    <t>Two meetings were conducted to discuss the SaaS project transition, current project completion, feature auditing, and the initial transfer of real data</t>
   </si>
 </sst>
 </file>
@@ -1655,19 +1661,29 @@
         <v>112</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" ht="132">
       <c r="A33" s="2">
         <v>28</v>
       </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="3"/>
+      <c r="B33" s="5">
+        <v>46295</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>113</v>
+      </c>
       <c r="E33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" s="2"/>
+        <v>26</v>
+      </c>
+      <c r="F33" s="2">
+        <v>8</v>
+      </c>
       <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
+      <c r="H33" s="3" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="2">

--- a/frontend/Frontend-Daily-Tracker.xlsx
+++ b/frontend/Frontend-Daily-Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\intern 2\Business-Listing\frontend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C098D1ED-FB8F-47C6-8CD0-395AF320E0CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B04C3738-F9CE-4614-A8A8-9ED9D310161A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="118">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -400,6 +400,15 @@
   </si>
   <si>
     <t>Two meetings were conducted to discuss the SaaS project transition, current project completion, feature auditing, and the initial transfer of real data</t>
+  </si>
+  <si>
+    <t>Finalized the frontend and backend integration by transitioning the application from demo data to real backend data in the main project files. Added new toggles and configuration controls to switch between demo and real data while keeping API details hidden from the frontend interface. Continued carrying out audits across the frontend to identify remaining issues and areas for improvement. Held a final project discussion with the backend developer to review the current integration, remaining work, and overall project status. Also planned the testing activities for the following day and reviewed the project structure to identify common and reusable files that could potentially be transferred into a future SaaS implementation.</t>
+  </si>
+  <si>
+    <t>feat: finalize backend integration, real data, audits, and SaaS preparation</t>
+  </si>
+  <si>
+    <t>Real backend data has been integrated into the main frontend implementation, with demo-to-real data switching added for development flexibility. Completed further frontend audits, discussed the final integration status with the backend developer, planned the upcoming testing phase, and identified reusable project files that could be carried forward into a SaaS implementation.</t>
   </si>
 </sst>
 </file>
@@ -1685,19 +1694,31 @@
         <v>114</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" ht="198">
       <c r="A34" s="2">
         <v>29</v>
       </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="3"/>
+      <c r="B34" s="5">
+        <v>46296</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>115</v>
+      </c>
       <c r="E34" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" s="2"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
+        <v>26</v>
+      </c>
+      <c r="F34" s="2">
+        <v>8</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="2">

--- a/frontend/Frontend-Daily-Tracker.xlsx
+++ b/frontend/Frontend-Daily-Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\intern 2\Business-Listing\frontend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B04C3738-F9CE-4614-A8A8-9ED9D310161A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0CC394B-30A0-4660-ACEB-E7138BD60BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="121">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -409,6 +409,15 @@
   </si>
   <si>
     <t>Real backend data has been integrated into the main frontend implementation, with demo-to-real data switching added for development flexibility. Completed further frontend audits, discussed the final integration status with the backend developer, planned the upcoming testing phase, and identified reusable project files that could be carried forward into a SaaS implementation.</t>
+  </si>
+  <si>
+    <t>Held an in-depth discussion regarding the future SaaS direction of the project and reviewed the changes required to make the current project structure suitable for further reuse and distribution. Updated the project JSON and lock JSON configuration files as part of the project setup and dependency configuration changes. Improved the website’s SEO implementation by adding structured data support using Schema.org JSON-LD, including a reusable structuredData.ts utility for generating structured data for the Homepage and Listing Detail pages and a reusable JsonLd.tsx component for safely rendering JSON-LD data. Also added a dedicated Google Maps loader to load the Maps JavaScript API and Places library efficiently through a shared promise while keeping the implementation compatible with server-side code. Continued reviewing and refining the project structure with future SaaS reuse in mind.</t>
+  </si>
+  <si>
+    <t>feat: add SEO structured data, maps loader, and project configuration</t>
+  </si>
+  <si>
+    <t>No blockers. Completed the planned SEO and technical improvements, including structured data and Google Maps loading infrastructure. Also held a detailed discussion about the future SaaS direction of the project and reviewed common project structures and configuration that could support future reuse.</t>
   </si>
 </sst>
 </file>
@@ -1720,19 +1729,31 @@
         <v>117</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" ht="237.6">
       <c r="A35" s="2">
         <v>30</v>
       </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="3"/>
+      <c r="B35" s="5">
+        <v>46297</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="E35" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" s="2"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
+        <v>26</v>
+      </c>
+      <c r="F35" s="2">
+        <v>8</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="2">

--- a/frontend/Frontend-Daily-Tracker.xlsx
+++ b/frontend/Frontend-Daily-Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\intern 2\Business-Listing\frontend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0CC394B-30A0-4660-ACEB-E7138BD60BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E58A632B-EE80-47F1-9157-519442328C72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="123">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -71,9 +71,6 @@
   </si>
   <si>
     <t>Week 7</t>
-  </si>
-  <si>
-    <t>Wire up config for dynamic content + responsive QA</t>
   </si>
   <si>
     <t>Week 8</t>
@@ -418,6 +415,15 @@
   </si>
   <si>
     <t>No blockers. Completed the planned SEO and technical improvements, including structured data and Google Maps loading infrastructure. Also held a detailed discussion about the future SaaS direction of the project and reviewed common project structures and configuration that could support future reuse.</t>
+  </si>
+  <si>
+    <t>Upgraded the Business Listing frontend from Next.js 14 to Next.js 16, including React 19 and the matching tools (ESLint, Vitest and TypeScript), and fixed the code that the upgrade broke. Turned on image optimisation so images load faster, and added a helper so uploaded images still show up even when the saved address points to an old localhost. Added new SEO pages for each category and each location, which refresh themselves every 5 minutes and are added to the sitemap. Pages with no listings are hidden from Google. Added a helper that keeps public data cached, a short listing summary and location matching, with tests for them. Made all open browser tabs show the same signed-in user. Also worked on the restaurant SaaS project: fixed the customer pages (home, menu, nav bar, coupon, cart, checkout map and order page), cleaned up the code, committed it and opened a pull request for review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feat: upgrade to Next.js 16, add category and location landing pages, and image URL helper   feat: home, menu, nav, coupon, cart, checkout map and order page fixes            </t>
+  </si>
+  <si>
+    <t>No blockers. Completed the Next.js 16 / React 19 migration of the listing frontend. Opened SaaS pull request PranavPoudel/Logicbit-Solution-Restaurant-Saas#20) and requested a review from the backend developer. Waiting on review feedback.</t>
   </si>
 </sst>
 </file>
@@ -907,7 +913,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -966,10 +972,10 @@
         <v>9</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F5" s="2">
         <v>5</v>
@@ -985,22 +991,22 @@
         <v>46259</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="2">
+        <v>8</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="2">
-        <v>8</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="198">
@@ -1011,22 +1017,22 @@
         <v>46260</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="2">
+        <v>8</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="2">
-        <v>8</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="172.2">
@@ -1037,22 +1043,22 @@
         <v>46261</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="E8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="2">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="2">
-        <v>8</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="172.2">
@@ -1063,22 +1069,22 @@
         <v>46262</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="E9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="2">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="2">
-        <v>8</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="159">
@@ -1089,22 +1095,22 @@
         <v>46264</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="2">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" s="2">
-        <v>8</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="184.8">
@@ -1118,19 +1124,19 @@
         <v>11</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="2">
+        <v>8</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11" s="2">
-        <v>8</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="184.8">
@@ -1141,22 +1147,22 @@
         <v>46266</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="2">
+        <v>8</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="2">
-        <v>8</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="H12" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="132">
@@ -1167,22 +1173,22 @@
         <v>46267</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="2">
+        <v>8</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" s="2">
-        <v>8</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="118.8">
@@ -1193,22 +1199,22 @@
         <v>46268</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="2">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F14" s="2">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="145.19999999999999">
@@ -1219,22 +1225,22 @@
         <v>46269</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="2">
+        <v>8</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F15" s="2">
-        <v>8</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="198">
@@ -1248,19 +1254,19 @@
         <v>12</v>
       </c>
       <c r="D16" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="2">
+        <v>8</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="2">
-        <v>8</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="H16" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="224.4">
@@ -1271,22 +1277,22 @@
         <v>46273</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D17" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="2">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F17" s="2">
-        <v>8</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="187.2">
@@ -1297,22 +1303,22 @@
         <v>46274</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="2">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F18" s="2">
-        <v>8</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="105.6">
@@ -1323,22 +1329,22 @@
         <v>46275</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="2">
+        <v>8</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F19" s="2">
-        <v>8</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="105.6">
@@ -1349,22 +1355,22 @@
         <v>46276</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="2">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F20" s="2">
-        <v>8</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="158.4">
@@ -1378,19 +1384,19 @@
         <v>13</v>
       </c>
       <c r="D21" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="2">
+        <v>8</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F21" s="2">
-        <v>8</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="224.4">
@@ -1401,22 +1407,22 @@
         <v>46280</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D22" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="2">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F22" s="2">
-        <v>8</v>
-      </c>
-      <c r="G22" s="3" t="s">
+      <c r="H22" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="158.4">
@@ -1427,22 +1433,22 @@
         <v>46281</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D23" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="2">
+        <v>8</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F23" s="2">
-        <v>8</v>
-      </c>
-      <c r="G23" s="3" t="s">
+      <c r="H23" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="158.4">
@@ -1450,25 +1456,25 @@
         <v>19</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="2">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F24" s="2">
-        <v>8</v>
-      </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="237.6">
@@ -1479,22 +1485,22 @@
         <v>46283</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D25" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="2">
+        <v>8</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F25" s="2">
-        <v>8</v>
-      </c>
-      <c r="G25" s="3" t="s">
+      <c r="H25" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="330">
@@ -1502,25 +1508,25 @@
         <v>21</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D26" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="2">
+        <v>8</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F26" s="2">
-        <v>8</v>
-      </c>
-      <c r="G26" s="3" t="s">
+      <c r="H26" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="250.8">
@@ -1531,22 +1537,22 @@
         <v>46287</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D27" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" s="2">
+        <v>8</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F27" s="2">
-        <v>8</v>
-      </c>
-      <c r="G27" s="3" t="s">
+      <c r="H27" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="290.39999999999998">
@@ -1557,22 +1563,22 @@
         <v>46288</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D28" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" s="2">
+        <v>8</v>
+      </c>
+      <c r="G28" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F28" s="2">
-        <v>8</v>
-      </c>
-      <c r="G28" s="3" t="s">
+      <c r="H28" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="316.8">
@@ -1583,22 +1589,22 @@
         <v>46289</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D29" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" s="2">
+        <v>8</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F29" s="2">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
+      <c r="H29" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="238.2">
@@ -1609,22 +1615,22 @@
         <v>46290</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D30" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" s="2">
+        <v>8</v>
+      </c>
+      <c r="G30" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F30" s="2">
-        <v>8</v>
-      </c>
-      <c r="G30" s="3" t="s">
+      <c r="H30" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="264">
@@ -1638,19 +1644,19 @@
         <v>15</v>
       </c>
       <c r="D31" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" s="2">
+        <v>8</v>
+      </c>
+      <c r="G31" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F31" s="2">
-        <v>8</v>
-      </c>
-      <c r="G31" s="3" t="s">
+      <c r="H31" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="250.8">
@@ -1661,22 +1667,22 @@
         <v>46294</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D32" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" s="2">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F32" s="2">
-        <v>8</v>
-      </c>
-      <c r="G32" s="3" t="s">
+      <c r="H32" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="132">
@@ -1687,20 +1693,20 @@
         <v>46295</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F33" s="2">
         <v>8</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="198">
@@ -1711,22 +1717,22 @@
         <v>46296</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D34" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34" s="2">
+        <v>8</v>
+      </c>
+      <c r="G34" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F34" s="2">
-        <v>8</v>
-      </c>
-      <c r="G34" s="3" t="s">
+      <c r="H34" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="237.6">
@@ -1737,41 +1743,49 @@
         <v>46297</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D35" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" s="2">
+        <v>8</v>
+      </c>
+      <c r="G35" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F35" s="2">
-        <v>8</v>
-      </c>
-      <c r="G35" s="3" t="s">
+      <c r="H35" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
+    </row>
+    <row r="36" spans="1:8" ht="237.6">
       <c r="A36" s="2">
         <v>31</v>
       </c>
-      <c r="B36" s="3"/>
+      <c r="B36" s="5">
+        <v>46300</v>
+      </c>
       <c r="C36" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" s="2"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="F36" s="2">
+        <v>8</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="2">
@@ -1835,10 +1849,10 @@
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>10</v>

--- a/frontend/Frontend-Daily-Tracker.xlsx
+++ b/frontend/Frontend-Daily-Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\intern 2\Business-Listing\frontend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E58A632B-EE80-47F1-9157-519442328C72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D1BC5F4-95CE-410E-A82C-5D00864CC4BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="126">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -424,6 +424,15 @@
   </si>
   <si>
     <t>No blockers. Completed the Next.js 16 / React 19 migration of the listing frontend. Opened SaaS pull request PranavPoudel/Logicbit-Solution-Restaurant-Saas#20) and requested a review from the backend developer. Waiting on review feedback.</t>
+  </si>
+  <si>
+    <t>Added owner notifications to the SaaS restaurant app. The bell in the owner topbar now opens a popup, and a full-screen view, showing new orders, rider requests and delivered orders. Owners can accept or reject orders, approve or reject a rider's request, and confirm completion after delivery. A toast message and a short chime now alert the owner when a new notification arrives. Built the rider approval flow: the owner approves a rider before the order goes out for delivery, and the rider portal now has Picked up, Start delivery and Mark delivered steps with a waiting-for-approval message. Added a rider card with Approve, Reject and Confirm complete buttons to the order detail page, and fixed the wrong item price and subtotal shown there. Added an "Auto-approve riders" switch to the Orders page so owners can choose between automatic and manual rider approval. On the backend, added a reject-rider endpoint so a rejected order goes back to other riders, and changed delivery so the owner confirms completion. Fixed the customer order page so it refreshes by itself, shows the right delivery partner details, and has a cancel button. Pulled in the team lead's latest owner dashboard changes and merged them with my work, then ran the full ordering flow end to end and pushed the branch. Also worked on Auto Hub fixes and finalized the Auto Hub website together with the backend developer. Held a meeting with the SaaS team leader about the gaps, issues and fixes in the project.</t>
+  </si>
+  <si>
+    <t>feat(owner): notifications bell, rider approval flow and auto-approve toggle</t>
+  </si>
+  <si>
+    <t>Completed the owner notification and rider approval work on top of the latest owner dashboard changes and pushed it for review. The customer order page fixes are still to be committed. Finalized the Auto Hub website with the backend developer, and went through the SaaS gaps and fixes with the team leader.</t>
   </si>
 </sst>
 </file>
@@ -1787,19 +1796,31 @@
         <v>122</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" ht="382.8">
       <c r="A37" s="2">
         <v>32</v>
       </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="3"/>
+      <c r="B37" s="5">
+        <v>46301</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>123</v>
+      </c>
       <c r="E37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" s="2"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="F37" s="2">
+        <v>8</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="2">

--- a/frontend/Frontend-Daily-Tracker.xlsx
+++ b/frontend/Frontend-Daily-Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\intern 2\Business-Listing\frontend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D1BC5F4-95CE-410E-A82C-5D00864CC4BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B218422-C9F2-43C6-8753-A63DF1E9943C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="129">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -433,6 +433,15 @@
   </si>
   <si>
     <t>Completed the owner notification and rider approval work on top of the latest owner dashboard changes and pushed it for review. The customer order page fixes are still to be committed. Finalized the Auto Hub website with the backend developer, and went through the SaaS gaps and fixes with the team leader.</t>
+  </si>
+  <si>
+    <t>Went through the whole SaaS restaurant project page by page in the browser (customer, owner, admin and rider pages, including phone-size screens) and made a list of the bugs and gaps for the team lead. Added a payment method popup at checkout: after pressing Place Order the customer picks Cash on Delivery, Card, Khalti or eSewa, and the options that aren't set up yet show the server's message instead of failing silently. Customers who aren't logged in are now sent to the login page before checkout. Replaced the browser's cancel order confirm box with a proper confirm dialog, and added a shared helper so popups keep focus inside them and stop the page scrolling behind. Fixed the map showing on top of popups. Fixed the customer account area: the Addresses tab could not save at all because of wrong field names, and it now has a map to pin the address; the profile shows and saves the name correctly; order history shows the restaurant and order number; and favourites show restaurant names. Moved the checkout address and map into one shared address picker used by both checkout and account. Cleaned up the new code with simplicity reviews. Merged the team lead's latest changes (auto-print on order accepted) into my branch, checked it compiles with no conflicts, and pushed it ready for a pull request. Also set up the Business Listing project in a new folder on the D drive: installed the backend and frontend packages, started a Docker Postgres database, ran all the migrations and added the starting categories.</t>
+  </si>
+  <si>
+    <t>feat(customer): payment popup, account fixes with map address picker, and order page updates</t>
+  </si>
+  <si>
+    <t>Pushed feature/customer-fixes merged with the latest main (no conflicts) and prepared the pull request for review. Listed the project's gaps for the team lead, including exposed password hashes in the delivery persons list, no automated tests, the failing production build, and the pages that still need fixing (phone layout for the owner dashboard, broken images on the owner menu, and missing admin pages). Business Listing is set up locally but still needs an admin account and the listing data imported.</t>
   </si>
 </sst>
 </file>
@@ -1822,19 +1831,31 @@
         <v>125</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" ht="409.2">
       <c r="A38" s="2">
         <v>33</v>
       </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="3"/>
+      <c r="B38" s="5">
+        <v>46302</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>126</v>
+      </c>
       <c r="E38" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" s="2"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="F38" s="2">
+        <v>8</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="2">

--- a/frontend/Frontend-Daily-Tracker.xlsx
+++ b/frontend/Frontend-Daily-Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\intern 2\Business-Listing\frontend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B218422-C9F2-43C6-8753-A63DF1E9943C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89689F67-0173-4D34-B259-3B68211D23C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="133">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -442,6 +442,19 @@
   </si>
   <si>
     <t>Pushed feature/customer-fixes merged with the latest main (no conflicts) and prepared the pull request for review. Listed the project's gaps for the team lead, including exposed password hashes in the delivery persons list, no automated tests, the failing production build, and the pages that still need fixing (phone layout for the owner dashboard, broken images on the owner menu, and missing admin pages). Business Listing is set up locally but still needs an admin account and the listing data imported.</t>
+  </si>
+  <si>
+    <t>Day4</t>
+  </si>
+  <si>
+    <t>fix(order): restore validate-coupon and reject-rider routes
+feat: favourites, admin owners and activity logs, PayPay checkout   chore(frontend): remove unused code and clsx dependency</t>
+  </si>
+  <si>
+    <t>Had a discussion about Auto Hub with the backend developer. I reviewed the whole project for unnecessary code, covering  the frontend. Checked the latest changes from the team lead and found that his auto-print commit had accidentally removed two server routes (the coupon preview at checkout and the owner's Reject rider), so both were returning errors. I restored them, tested them against the running server, and pushed the fix. Made the heart on restaurant cards real: it now saves to the customer's favourites, fills in correctly after a refresh, and sends logged-out visitors to the login page. Built two new admin pages. The first is Owners &amp; Cash Flow, which shows orders, sales, platform commission and payout per owner and per restaurant, with owners who have several restaurants expandable. The second is Activity Logs, with paging and a restaurant name on every entry.At checkout I removed Khalti and added PayPay, with its own PayPay payment method on the server replaced the customer's cancel-order button with a note to call the restaurant, and deleted the confirm dialog and cancel code that were no longer used. Merged Rounak's delivery module into my branch with no conflicts and tested everything together: 14 server checks and 9 page loads pass. Ran simplicity reviews on all of it. Also reviewed the Business Listing project for unnecessary code, removed the unused files, functions and one unused package from the frontend, checked that it builds and its 43 tests pass, and pushed.</t>
+  </si>
+  <si>
+    <t>No blockers. Pushed feature/customer-fixes on top of the latest main, ready for a pull request. The PR needs a prisma db push because of the new PayPay payment method. Only cash on delivery takes payments for now; Card, eSewa and PayPay are placeholders until a payment provider is set up. Login location in the activity logs is not built yet. It needs the login IP to be saved first. Also pushed fix(order): restore validate-coupon and reject-rider routes for the two routes, and chore(frontend): remove unused code and clsx dependency in Business Listing.</t>
   </si>
 </sst>
 </file>
@@ -1831,7 +1844,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="409.2">
+    <row r="38" spans="1:8" ht="396">
       <c r="A38" s="2">
         <v>33</v>
       </c>
@@ -1857,19 +1870,31 @@
         <v>128</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" ht="396">
       <c r="A39" s="2">
         <v>34</v>
       </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="3"/>
+      <c r="B39" s="5">
+        <v>46303</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>131</v>
+      </c>
       <c r="E39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F39" s="2">
         <v>10</v>
       </c>
-      <c r="F39" s="2"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
+      <c r="G39" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="2">

--- a/frontend/Frontend-Daily-Tracker.xlsx
+++ b/frontend/Frontend-Daily-Tracker.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\intern 2\Business-Listing\frontend\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89689F67-0173-4D34-B259-3B68211D23C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264"/>
   </bookViews>
   <sheets>
     <sheet name="Daily Tracker" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="136">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -456,12 +455,42 @@
   <si>
     <t>No blockers. Pushed feature/customer-fixes on top of the latest main, ready for a pull request. The PR needs a prisma db push because of the new PayPay payment method. Only cash on delivery takes payments for now; Card, eSewa and PayPay are placeholders until a payment provider is set up. Login location in the activity logs is not built yet. It needs the login IP to be saved first. Also pushed fix(order): restore validate-coupon and reject-rider routes for the two routes, and chore(frontend): remove unused code and clsx dependency in Business Listing.</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tested the project setup on a clean environment by restoring the database from the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>.dmp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> file and following the restore guide. Ran Lighthouse audits on mobile and desktop to check performance, accessibility, best practices and SEO. Tested Google and Facebook login end to end, including the sign-in redirect and the account being created or linked in the app. Tested the email features, including password reset and owner announcements, to check that emails are sent and the links work.</t>
+    </r>
+  </si>
+  <si>
+    <t>docs: added daily tracker spreadsheet</t>
+  </si>
+  <si>
+    <t>Day5</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -504,6 +533,12 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -563,7 +598,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -598,6 +633,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -928,7 +966,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H45"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
@@ -1014,7 +1052,7 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="1:8" ht="184.8">
+    <row r="6" spans="1:8" ht="171.6">
       <c r="A6" s="2">
         <v>1</v>
       </c>
@@ -1896,18 +1934,28 @@
         <v>132</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" ht="144.6">
       <c r="A40" s="2">
         <v>35</v>
       </c>
-      <c r="B40" s="3"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="3"/>
+      <c r="B40" s="5">
+        <v>46304</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>133</v>
+      </c>
       <c r="E40" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" s="2"/>
-      <c r="G40" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="F40" s="2">
+        <v>6</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>134</v>
+      </c>
       <c r="H40" s="3"/>
     </row>
     <row r="41" spans="1:8" ht="26.4">
@@ -2004,7 +2052,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="E5:E45" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="E5:E45">
       <formula1>"Todo,In Progress,Blocked,Complete"</formula1>
     </dataValidation>
   </dataValidations>

--- a/frontend/Frontend-Daily-Tracker.xlsx
+++ b/frontend/Frontend-Daily-Tracker.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\intern 2\Business-Listing\frontend\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11270CA6-1070-4DA8-B88C-44D3153CDCE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Daily Tracker" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="138">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -73,9 +74,6 @@
   </si>
   <si>
     <t>Week 8</t>
-  </si>
-  <si>
-    <t>Bug fixing, content polish, deployment, final presentation</t>
   </si>
   <si>
     <t xml:space="preserve">Frontend Developer #3 — Business Listing </t>
@@ -456,41 +454,29 @@
     <t>No blockers. Pushed feature/customer-fixes on top of the latest main, ready for a pull request. The PR needs a prisma db push because of the new PayPay payment method. Only cash on delivery takes payments for now; Card, eSewa and PayPay are placeholders until a payment provider is set up. Login location in the activity logs is not built yet. It needs the login IP to be saved first. Also pushed fix(order): restore validate-coupon and reject-rider routes for the two routes, and chore(frontend): remove unused code and clsx dependency in Business Listing.</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Tested the project setup on a clean environment by restoring the database from the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>.dmp</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> file and following the restore guide. Ran Lighthouse audits on mobile and desktop to check performance, accessibility, best practices and SEO. Tested Google and Facebook login end to end, including the sign-in redirect and the account being created or linked in the app. Tested the email features, including password reset and owner announcements, to check that emails are sent and the links work.</t>
-    </r>
-  </si>
-  <si>
     <t>docs: added daily tracker spreadsheet</t>
   </si>
   <si>
     <t>Day5</t>
+  </si>
+  <si>
+    <t>Tested the project setup on a clean environment by restoring the database from the .dmp file and following the restore guide. Ran Lighthouse audits on mobile and desktop to check performance, accessibility, best practices and SEO. Tested Google and Facebook login end to end, including the sign-in redirect and the account being created or linked in the app. Tested the email features, including password reset and owner announcements, to check that emails are sent and the links work.</t>
+  </si>
+  <si>
+    <t>Made the customer side of the SaaS easier to use, working through the review feedback. The dish popup is now two columns and shows the ingredients, spice level and allergen information, so a customer can see what’s in a dish before adding it. The menu is now one long scroll: the category bar at the top stays in view, follows where you are, and jumps to a category when tapped, and each category shows 12 dishes at a time with a “Show more” button. At checkout I added a hint under the address, a plain explanation of the delivery fee, and a line under the grey Place Order button saying what’s missing. The Delivery and Pickup switch now slides smoothly, and the Pickup page lines up in one column under it. The coupon box moved under the order summary, and I fixed its cut-off hint text. The restaurant footer no longer shows made-up opening hours and now shows on the cart and checkout pages too. The order page has a new wide layout with a plain message for each status, the pickup address, a price breakdown and a Receipt button in the order summary. I also pulled in the team lead’s latest PayPay and admin changes and fixed the one conflict in checkout, then did a clean-up pass on everything. I reviewed the owner orders page and listed what needs fixing, and looked into why a restaurant’s chosen colours never show on its customer pages.</t>
+  </si>
+  <si>
+    <t>feat(customer): dish popup, coupon in cart, order page and checkout redesign</t>
+  </si>
+  <si>
+    <t>No blockers. Pushed feature/customer-fixes on top of the latest main, ready for a pull request. The PR needs a prisma db push because of the new ingredients and allergen columns. The restaurant colours are saved by the owner but the server never sends them to customers, so showing them needs a small server change to be agreed. The order page can’t show the restaurant’s phone number for cancelling because the server doesn’t send it yet. Still to do: measure menu speed on a large menu, analytics events, and the owner orders page fixes.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -533,12 +519,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial Unicode MS"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -633,7 +613,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -966,7 +946,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H45"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
@@ -982,7 +962,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -1041,10 +1021,10 @@
         <v>9</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F5" s="2">
         <v>5</v>
@@ -1052,7 +1032,7 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="1:8" ht="171.6">
+    <row r="6" spans="1:8" ht="184.8">
       <c r="A6" s="2">
         <v>1</v>
       </c>
@@ -1060,22 +1040,22 @@
         <v>46259</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="2">
+        <v>8</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="2">
-        <v>8</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="198">
@@ -1086,22 +1066,22 @@
         <v>46260</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="2">
+        <v>8</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="2">
-        <v>8</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="172.2">
@@ -1112,22 +1092,22 @@
         <v>46261</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="E8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="2">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="2">
-        <v>8</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="172.2">
@@ -1138,22 +1118,22 @@
         <v>46262</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="E9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="2">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="2">
-        <v>8</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="159">
@@ -1164,22 +1144,22 @@
         <v>46264</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="2">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="2">
-        <v>8</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="184.8">
@@ -1193,19 +1173,19 @@
         <v>11</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="2">
+        <v>8</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="2">
-        <v>8</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="184.8">
@@ -1216,22 +1196,22 @@
         <v>46266</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="2">
+        <v>8</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="2">
-        <v>8</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="H12" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="132">
@@ -1242,22 +1222,22 @@
         <v>46267</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="2">
+        <v>8</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="2">
-        <v>8</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="118.8">
@@ -1268,22 +1248,22 @@
         <v>46268</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="2">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="2">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="145.19999999999999">
@@ -1294,22 +1274,22 @@
         <v>46269</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="2">
+        <v>8</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="2">
-        <v>8</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="198">
@@ -1323,19 +1303,19 @@
         <v>12</v>
       </c>
       <c r="D16" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" s="2">
+        <v>8</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="2">
-        <v>8</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="H16" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="224.4">
@@ -1346,22 +1326,22 @@
         <v>46273</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D17" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="2">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="2">
-        <v>8</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="187.2">
@@ -1372,22 +1352,22 @@
         <v>46274</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D18" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="2">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="2">
-        <v>8</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="105.6">
@@ -1398,22 +1378,22 @@
         <v>46275</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="2">
+        <v>8</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="2">
-        <v>8</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="105.6">
@@ -1424,22 +1404,22 @@
         <v>46276</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F20" s="2">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="2">
-        <v>8</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="158.4">
@@ -1453,19 +1433,19 @@
         <v>13</v>
       </c>
       <c r="D21" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21" s="2">
+        <v>8</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="2">
-        <v>8</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="10" t="s">
         <v>74</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="224.4">
@@ -1476,22 +1456,22 @@
         <v>46280</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D22" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F22" s="2">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="2">
-        <v>8</v>
-      </c>
-      <c r="G22" s="3" t="s">
+      <c r="H22" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="158.4">
@@ -1502,22 +1482,22 @@
         <v>46281</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D23" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F23" s="2">
+        <v>8</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="2">
-        <v>8</v>
-      </c>
-      <c r="G23" s="3" t="s">
+      <c r="H23" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="158.4">
@@ -1525,25 +1505,25 @@
         <v>19</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F24" s="2">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="2">
-        <v>8</v>
-      </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="237.6">
@@ -1554,22 +1534,22 @@
         <v>46283</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D25" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F25" s="2">
+        <v>8</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" s="2">
-        <v>8</v>
-      </c>
-      <c r="G25" s="3" t="s">
+      <c r="H25" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="330">
@@ -1577,25 +1557,25 @@
         <v>21</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D26" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F26" s="2">
+        <v>8</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="2">
-        <v>8</v>
-      </c>
-      <c r="G26" s="3" t="s">
+      <c r="H26" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="250.8">
@@ -1606,22 +1586,22 @@
         <v>46287</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D27" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F27" s="2">
+        <v>8</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F27" s="2">
-        <v>8</v>
-      </c>
-      <c r="G27" s="3" t="s">
+      <c r="H27" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="290.39999999999998">
@@ -1632,22 +1612,22 @@
         <v>46288</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D28" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F28" s="2">
+        <v>8</v>
+      </c>
+      <c r="G28" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" s="2">
-        <v>8</v>
-      </c>
-      <c r="G28" s="3" t="s">
+      <c r="H28" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="316.8">
@@ -1658,22 +1638,22 @@
         <v>46289</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D29" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" s="2">
+        <v>8</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" s="2">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
+      <c r="H29" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="238.2">
@@ -1684,22 +1664,22 @@
         <v>46290</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D30" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" s="2">
+        <v>8</v>
+      </c>
+      <c r="G30" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F30" s="2">
-        <v>8</v>
-      </c>
-      <c r="G30" s="3" t="s">
+      <c r="H30" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="264">
@@ -1713,19 +1693,19 @@
         <v>15</v>
       </c>
       <c r="D31" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F31" s="2">
+        <v>8</v>
+      </c>
+      <c r="G31" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F31" s="2">
-        <v>8</v>
-      </c>
-      <c r="G31" s="3" t="s">
+      <c r="H31" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="250.8">
@@ -1736,22 +1716,22 @@
         <v>46294</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D32" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F32" s="2">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F32" s="2">
-        <v>8</v>
-      </c>
-      <c r="G32" s="3" t="s">
+      <c r="H32" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="132">
@@ -1762,20 +1742,20 @@
         <v>46295</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F33" s="2">
         <v>8</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="198">
@@ -1786,22 +1766,22 @@
         <v>46296</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D34" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F34" s="2">
+        <v>8</v>
+      </c>
+      <c r="G34" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F34" s="2">
-        <v>8</v>
-      </c>
-      <c r="G34" s="3" t="s">
+      <c r="H34" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="237.6">
@@ -1812,22 +1792,22 @@
         <v>46297</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D35" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F35" s="2">
+        <v>8</v>
+      </c>
+      <c r="G35" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F35" s="2">
-        <v>8</v>
-      </c>
-      <c r="G35" s="3" t="s">
+      <c r="H35" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="237.6">
@@ -1841,19 +1821,19 @@
         <v>16</v>
       </c>
       <c r="D36" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F36" s="2">
+        <v>8</v>
+      </c>
+      <c r="G36" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F36" s="2">
-        <v>8</v>
-      </c>
-      <c r="G36" s="3" t="s">
+      <c r="H36" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="382.8">
@@ -1864,22 +1844,22 @@
         <v>46301</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D37" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F37" s="2">
+        <v>8</v>
+      </c>
+      <c r="G37" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F37" s="2">
-        <v>8</v>
-      </c>
-      <c r="G37" s="3" t="s">
+      <c r="H37" s="3" t="s">
         <v>124</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="396">
@@ -1890,22 +1870,22 @@
         <v>46302</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D38" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F38" s="2">
+        <v>8</v>
+      </c>
+      <c r="G38" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F38" s="2">
-        <v>8</v>
-      </c>
-      <c r="G38" s="3" t="s">
+      <c r="H38" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="396">
@@ -1916,25 +1896,25 @@
         <v>46303</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F39" s="2">
         <v>10</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="144.6">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="132">
       <c r="A40" s="2">
         <v>35</v>
       </c>
@@ -1942,39 +1922,47 @@
         <v>46304</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F40" s="2">
         <v>6</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H40" s="3"/>
     </row>
-    <row r="41" spans="1:8" ht="26.4">
+    <row r="41" spans="1:8" ht="356.4">
       <c r="A41" s="2">
         <v>36</v>
       </c>
-      <c r="B41" s="3"/>
+      <c r="B41" s="5">
+        <v>46307</v>
+      </c>
       <c r="C41" s="4" t="s">
         <v>17</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>18</v>
+        <v>135</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" s="2"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="F41" s="2">
+        <v>9</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="2">
@@ -2052,7 +2040,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="E5:E45">
+    <dataValidation type="list" sqref="E5:E45" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Todo,In Progress,Blocked,Complete"</formula1>
     </dataValidation>
   </dataValidations>

--- a/frontend/Frontend-Daily-Tracker.xlsx
+++ b/frontend/Frontend-Daily-Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\intern 2\Business-Listing\frontend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11270CA6-1070-4DA8-B88C-44D3153CDCE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6046059A-83F6-4B24-87F4-7F250E98254F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="141">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -470,6 +470,15 @@
   </si>
   <si>
     <t>No blockers. Pushed feature/customer-fixes on top of the latest main, ready for a pull request. The PR needs a prisma db push because of the new ingredients and allergen columns. The restaurant colours are saved by the owner but the server never sends them to customers, so showing them needs a small server change to be agreed. The order page can’t show the restaurant’s phone number for cancelling because the server doesn’t send it yet. Still to do: measure menu speed on a large menu, analytics events, and the owner orders page fixes.</t>
+  </si>
+  <si>
+    <t>Kept working through the meeting feedback on the customer and owner sides. The “20% off” popup and each restaurant’s own popup are now small cards in the bottom-left corner instead of covering the whole page, and a restaurant’s popup only shows once per visit. Owners can now give each popup a type, with a limit of 3 of their own promotions and 1 external ad active at a time, and the server enforces it. Each restaurant’s own colours now show on its page, buttons, tabs, cart bar and footer. Owners can add a phone number and a refund policy in Settings. The phone number shows in the footer and in the order page’s cancel note, and the refund policy shows at checkout and on the order page. The customer account page was redesigned with a left-hand menu, and it has a new Transactions tab showing payments and refunds. Order history now has All, Active, Completed and Cancelled categories, and the order page has a “Back to orders” link. Owners can also add a single extra like “Extra cheese” without making a whole group, and I redesigned the Modifiers screen and fixed its help text. Allergen warnings are now a clear red box, and the cart panel shows each dish on one tidy row. I ran clean-up passes on all of it and tested each change in the browser. I also committed and pushed it, rewrote the pull request description, and closed the servers.</t>
+  </si>
+  <si>
+    <t>feat(customer,owner): account page, popup limits, single modifiers, refund policy and restaurant theming</t>
+  </si>
+  <si>
+    <t>No blockers. Pushed to feature/customer-fixes, which updates the open pull request #32. The PR needs a prisma db push because of three new columns: the restaurant’s phone, the restaurant’s refund policy, and the popup type. The two things I flagged yesterday are now done with small server additions: the restaurant’s colours and phone number are now sent to customers. Still to do: menu subcategories (this needs a parent-category field on the server, so it should be agreed with the team lead first), phone-width checks on the owner pages, a “you already rated this” state on the order page, analytics events, and the owner orders page fixes.</t>
   </si>
 </sst>
 </file>
@@ -610,12 +619,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -961,28 +970,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="2" spans="1:8" ht="16.05" customHeight="1">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
     </row>
     <row r="4" spans="1:8" ht="22.05" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -1924,7 +1933,7 @@
       <c r="C40" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D40" s="14" t="s">
+      <c r="D40" s="11" t="s">
         <v>134</v>
       </c>
       <c r="E40" s="2" t="s">
@@ -1964,19 +1973,31 @@
         <v>137</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" ht="356.4">
       <c r="A42" s="2">
         <v>37</v>
       </c>
-      <c r="B42" s="3"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="3"/>
+      <c r="B42" s="5">
+        <v>46308</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>138</v>
+      </c>
       <c r="E42" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" s="2"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="F42" s="2">
+        <v>9</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="2">

--- a/frontend/Frontend-Daily-Tracker.xlsx
+++ b/frontend/Frontend-Daily-Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\intern 2\Business-Listing\frontend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6046059A-83F6-4B24-87F4-7F250E98254F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55FA5B0A-A483-4D5F-BAAB-5EC43E868412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="143">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -479,6 +479,12 @@
   </si>
   <si>
     <t>No blockers. Pushed to feature/customer-fixes, which updates the open pull request #32. The PR needs a prisma db push because of three new columns: the restaurant’s phone, the restaurant’s refund policy, and the popup type. The two things I flagged yesterday are now done with small server additions: the restaurant’s colours and phone number are now sent to customers. Still to do: menu subcategories (this needs a parent-category field on the server, so it should be agreed with the team lead first), phone-width checks on the owner pages, a “you already rated this” state on the order page, analytics events, and the owner orders page fixes.</t>
+  </si>
+  <si>
+    <t>Held a discussion with the Auto Hub backend developer about login and auditing. We talked about storing passwords safely using hashing and salting, recording login attempts and account actions in an audit log, adding Google Analytics to see how people use the site, and showing that data as graphs on a dashboard. I also spoke with the other frontend developer about the new design changes the project needs. Checked GitHub for new changes: the pull request for my customer, owner and account work was merged into main by the team lead, and a teammate has started a new branch with header and tap-target improvements. Added pagination to the customer order history. Orders now show 10 per page with Previous and Next buttons and a “Page 1 of N” label, switching between All, Active, Completed and Cancelled goes back to page 1, and the counts still cover all orders. I built it as a small reusable pager component, and it passes the type check and lint. For the design changes, I put together some design inspiration and example pages for the home, menu, cart and order screens to discuss with the team. These are only references and nothing in the real project was changed.</t>
+  </si>
+  <si>
+    <t>No blockers. The pagination is done but not committed yet. It will go on a new branch from the updated main so it isn’t mixed with the merged work. It is client-side for now, because the server’s order list still returns every order; true server-side paging would need an API change agreed with the team lead. Next: agree the audit log and analytics approach with the backend developer, decide with the other frontend developer which design changes to build first, and test the pagination in the browser with enough test orders.</t>
   </si>
 </sst>
 </file>
@@ -1947,7 +1953,7 @@
       </c>
       <c r="H40" s="3"/>
     </row>
-    <row r="41" spans="1:8" ht="356.4">
+    <row r="41" spans="1:8" ht="343.2">
       <c r="A41" s="2">
         <v>36</v>
       </c>
@@ -1999,19 +2005,29 @@
         <v>140</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" ht="316.8">
       <c r="A43" s="2">
         <v>38</v>
       </c>
-      <c r="B43" s="3"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="3"/>
+      <c r="B43" s="5">
+        <v>46309</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>141</v>
+      </c>
       <c r="E43" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" s="2"/>
+        <v>24</v>
+      </c>
+      <c r="F43" s="2">
+        <v>8</v>
+      </c>
       <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
+      <c r="H43" s="3" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="2">

--- a/frontend/Frontend-Daily-Tracker.xlsx
+++ b/frontend/Frontend-Daily-Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\intern 2\Business-Listing\frontend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55FA5B0A-A483-4D5F-BAAB-5EC43E868412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4AB6FD9-4423-4773-BD4A-8F8E4B9C2469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="146">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -485,6 +485,15 @@
   </si>
   <si>
     <t>No blockers. The pagination is done but not committed yet. It will go on a new branch from the updated main so it isn’t mixed with the merged work. It is client-side for now, because the server’s order list still returns every order; true server-side paging would need an API change agreed with the team lead. Next: agree the audit log and analytics approach with the backend developer, decide with the other frontend developer which design changes to build first, and test the pagination in the browser with enough test orders.</t>
+  </si>
+  <si>
+    <t>Built third-party delivery services for the SaaS restaurant app. I first looked at how restaurants usually work with delivery companies like Uber Direct and Wolt Drive, and at how the project handles delivery today. On the owner side, the Delivery Persons page now has a Delivery Services section with an Add button and popup. The owner picks a company (Uber Eats, Uber Direct, Pathao, Foodmandu, Wolt, DoorDash or another), then connects it either by logging in on the company’s own site or by entering API keys. Each service shows a status (not connected, connected or failed) with Connect, Test connection and Disconnect, and the owner can edit the contact, account ID, fee and notes, turn a service on or off, and remove it with a proper confirm popup instead of the browser one. It has loading and empty states. On the admin side, the Deliveries page has a new Delivery Services tab showing which restaurants work with which companies. On the server I added a new table and endpoints to list, add, edit and delete services, plus one for the admin list. I set up the connection screens as a framework for the backend developers, who will build the real connection, test and login redirect. On the checkout page I added support for courier delivery prices: it shows who is delivering, shows the server’s reason when delivery isn’t available, refreshes the price when it expires, and sends the quote with the order. I also finished the order history pagination. I improved the layout and styling of the new screens with the UI/UX guidelines, ran two simplicity clean-ups, tested everything in the browser as owner, admin and customer, committed it, merged the latest main into my branch and pushed it.</t>
+  </si>
+  <si>
+    <t>No blockers. Pushed to feature/customer-fixes, ready for me to open the pull request. The PR needs a prisma db push because of the new delivery services table. The Connect, Test and Disconnect buttons and the login redirect show “not available yet” until the backend developers build those endpoints, and the checkout price fields stay unused until the server returns them. Not built yet: sending orders to a delivery company, and connection status in the admin tab. Next: open the pull request and agree the connection endpoints with the backend team.</t>
+  </si>
+  <si>
+    <t>feat(customer,owner,admin): delivery services, checkout courier quotes and order history pagination</t>
   </si>
 </sst>
 </file>
@@ -2029,19 +2038,31 @@
         <v>142</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" ht="409.6">
       <c r="A44" s="2">
         <v>39</v>
       </c>
-      <c r="B44" s="3"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="3"/>
+      <c r="B44" s="5">
+        <v>46310</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>143</v>
+      </c>
       <c r="E44" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" s="2"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="F44" s="2">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="2">

--- a/frontend/Frontend-Daily-Tracker.xlsx
+++ b/frontend/Frontend-Daily-Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\intern 2\Business-Listing\frontend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4AB6FD9-4423-4773-BD4A-8F8E4B9C2469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D4EFB69-B83B-4564-8F74-1C475DED4058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="148">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -50,9 +50,6 @@
   </si>
   <si>
     <t>Week 1</t>
-  </si>
-  <si>
-    <t>Todo</t>
   </si>
   <si>
     <t>Week 2</t>
@@ -494,6 +491,15 @@
   </si>
   <si>
     <t>feat(customer,owner,admin): delivery services, checkout courier quotes and order history pagination</t>
+  </si>
+  <si>
+    <t>Continued developing the customer-side frontend of the Restaurant SaaS, merging the Figma-designed pages into the project’s own structure and theme configuration. Replaced the placeholder trending dishes with real data from a new backend endpoint that ranks the most-ordered dishes of the last 30 days, and made the Add button open the restaurant’s menu with the dish popup already open. Built the missing home and menu sections from the Figma designs, including How It Works, Why LogicBit, Signature Dishes, larger Popular Categories icon tiles, a grid/list/table view toggle, Reviews with a rating summary, filters and paging, Similar Restaurants using the standard restaurant card, and a Find Us section with an illustrated map and a toggle to the real map. Moved the hero, step and fallback dish images into the theme config and connected category images, homepage banners and popup ads to what owners and admins set. Made owner accent colours apply to the toggles and other accents on a restaurant’s page. Added spice level, “Customisable” and allergen tags to the dish cards. Created a homepage banner, a popup and a search boost ad to confirm they show on the home page, then restyled the banner cards to match the rest of the site. Cleaned up unused files and translation keys, ran code-quality audits, and prepared a project zip for handover. Compared the project against the team repository, found that it differed from the latest main in some customer pages and in unrelated delivery work, and merged only the customer-side files on top of main. After a type-check, committed the result and pushed it to a new branch, customer-redesign, without changing main.</t>
+  </si>
+  <si>
+    <t>feat(customer): redesign customer pages with theme-driven home, menu and restaurant sections</t>
+  </si>
+  <si>
+    <t>No blockers. The branch is pushed to the team repository, and no pull request is open yet. Where our customer pages overlapped with recent changes on main, our version was used. The delivery and owner/admin code was left out. The branch type-checks, with 2 old errors in files we didn’t touch, but it hasn’t been run in the browser. The owner image upload and real customer reviews are untested because the database has no reviews yet.</t>
   </si>
 </sst>
 </file>
@@ -986,7 +992,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
       <c r="A1" s="14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -1045,10 +1051,10 @@
         <v>9</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F5" s="2">
         <v>5</v>
@@ -1064,22 +1070,22 @@
         <v>46259</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="2">
+        <v>8</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="2">
-        <v>8</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="198">
@@ -1090,22 +1096,22 @@
         <v>46260</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="2">
+        <v>8</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="2">
-        <v>8</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="172.2">
@@ -1116,22 +1122,22 @@
         <v>46261</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="E8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="2">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="2">
-        <v>8</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="172.2">
@@ -1142,22 +1148,22 @@
         <v>46262</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="E9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="2">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="2">
-        <v>8</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="159">
@@ -1168,22 +1174,22 @@
         <v>46264</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="2">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" s="2">
-        <v>8</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="184.8">
@@ -1194,22 +1200,22 @@
         <v>46265</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="2">
+        <v>8</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="2">
-        <v>8</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="184.8">
@@ -1220,25 +1226,25 @@
         <v>46266</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="2">
+        <v>8</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" s="2">
-        <v>8</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="H12" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="132">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="145.19999999999999">
       <c r="A13" s="2">
         <v>8</v>
       </c>
@@ -1246,22 +1252,22 @@
         <v>46267</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="2">
+        <v>8</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F13" s="2">
-        <v>8</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="118.8">
@@ -1272,25 +1278,25 @@
         <v>46268</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="2">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="2">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="145.19999999999999">
+    </row>
+    <row r="15" spans="1:8" ht="158.4">
       <c r="A15" s="2">
         <v>10</v>
       </c>
@@ -1298,25 +1304,25 @@
         <v>46269</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="2">
+        <v>8</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F15" s="2">
-        <v>8</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="198">
+    </row>
+    <row r="16" spans="1:8" ht="211.2">
       <c r="A16" s="2">
         <v>11</v>
       </c>
@@ -1324,22 +1330,22 @@
         <v>46272</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D16" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="2">
+        <v>8</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F16" s="2">
-        <v>8</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="H16" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="224.4">
@@ -1350,22 +1356,22 @@
         <v>46273</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D17" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" s="2">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F17" s="2">
-        <v>8</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="187.2">
@@ -1376,22 +1382,22 @@
         <v>46274</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D18" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" s="2">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F18" s="2">
-        <v>8</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="105.6">
@@ -1402,22 +1408,22 @@
         <v>46275</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" s="2">
+        <v>8</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F19" s="2">
-        <v>8</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="105.6">
@@ -1428,22 +1434,22 @@
         <v>46276</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" s="2">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F20" s="2">
-        <v>8</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="158.4">
@@ -1454,22 +1460,22 @@
         <v>46279</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D21" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F21" s="2">
+        <v>8</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F21" s="2">
-        <v>8</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="10" t="s">
         <v>73</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="224.4">
@@ -1480,22 +1486,22 @@
         <v>46280</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D22" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" s="2">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F22" s="2">
-        <v>8</v>
-      </c>
-      <c r="G22" s="3" t="s">
+      <c r="H22" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="158.4">
@@ -1506,22 +1512,22 @@
         <v>46281</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D23" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" s="2">
+        <v>8</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F23" s="2">
-        <v>8</v>
-      </c>
-      <c r="G23" s="3" t="s">
+      <c r="H23" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="158.4">
@@ -1529,25 +1535,25 @@
         <v>19</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F24" s="2">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F24" s="2">
-        <v>8</v>
-      </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="237.6">
@@ -1558,22 +1564,22 @@
         <v>46283</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D25" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F25" s="2">
+        <v>8</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F25" s="2">
-        <v>8</v>
-      </c>
-      <c r="G25" s="3" t="s">
+      <c r="H25" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="330">
@@ -1581,25 +1587,25 @@
         <v>21</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26" s="3" t="s">
+      <c r="E26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F26" s="2">
+        <v>8</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F26" s="2">
-        <v>8</v>
-      </c>
-      <c r="G26" s="3" t="s">
+      <c r="H26" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="250.8">
@@ -1610,22 +1616,22 @@
         <v>46287</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D27" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F27" s="2">
+        <v>8</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F27" s="2">
-        <v>8</v>
-      </c>
-      <c r="G27" s="3" t="s">
+      <c r="H27" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="290.39999999999998">
@@ -1636,22 +1642,22 @@
         <v>46288</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D28" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" s="2">
+        <v>8</v>
+      </c>
+      <c r="G28" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F28" s="2">
-        <v>8</v>
-      </c>
-      <c r="G28" s="3" t="s">
+      <c r="H28" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="316.8">
@@ -1662,22 +1668,22 @@
         <v>46289</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D29" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F29" s="2">
+        <v>8</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F29" s="2">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
+      <c r="H29" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="238.2">
@@ -1688,22 +1694,22 @@
         <v>46290</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D30" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F30" s="2">
+        <v>8</v>
+      </c>
+      <c r="G30" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F30" s="2">
-        <v>8</v>
-      </c>
-      <c r="G30" s="3" t="s">
+      <c r="H30" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="264">
@@ -1714,22 +1720,22 @@
         <v>46293</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D31" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F31" s="2">
+        <v>8</v>
+      </c>
+      <c r="G31" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F31" s="2">
-        <v>8</v>
-      </c>
-      <c r="G31" s="3" t="s">
+      <c r="H31" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="250.8">
@@ -1740,22 +1746,22 @@
         <v>46294</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D32" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F32" s="2">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F32" s="2">
-        <v>8</v>
-      </c>
-      <c r="G32" s="3" t="s">
+      <c r="H32" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="132">
@@ -1766,20 +1772,20 @@
         <v>46295</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F33" s="2">
         <v>8</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="198">
@@ -1790,22 +1796,22 @@
         <v>46296</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D34" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F34" s="2">
+        <v>8</v>
+      </c>
+      <c r="G34" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F34" s="2">
-        <v>8</v>
-      </c>
-      <c r="G34" s="3" t="s">
+      <c r="H34" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="237.6">
@@ -1816,22 +1822,22 @@
         <v>46297</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D35" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F35" s="2">
+        <v>8</v>
+      </c>
+      <c r="G35" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F35" s="2">
-        <v>8</v>
-      </c>
-      <c r="G35" s="3" t="s">
+      <c r="H35" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="237.6">
@@ -1842,22 +1848,22 @@
         <v>46300</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D36" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F36" s="2">
+        <v>8</v>
+      </c>
+      <c r="G36" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F36" s="2">
-        <v>8</v>
-      </c>
-      <c r="G36" s="3" t="s">
+      <c r="H36" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="382.8">
@@ -1868,22 +1874,22 @@
         <v>46301</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D37" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F37" s="2">
+        <v>8</v>
+      </c>
+      <c r="G37" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F37" s="2">
-        <v>8</v>
-      </c>
-      <c r="G37" s="3" t="s">
+      <c r="H37" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="396">
@@ -1894,22 +1900,22 @@
         <v>46302</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D38" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F38" s="2">
+        <v>8</v>
+      </c>
+      <c r="G38" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F38" s="2">
-        <v>8</v>
-      </c>
-      <c r="G38" s="3" t="s">
+      <c r="H38" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="396">
@@ -1920,22 +1926,22 @@
         <v>46303</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F39" s="2">
         <v>10</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="132">
@@ -1946,19 +1952,19 @@
         <v>46304</v>
       </c>
       <c r="C40" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D40" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D40" s="11" t="s">
-        <v>134</v>
-      </c>
       <c r="E40" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F40" s="2">
         <v>6</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H40" s="3"/>
     </row>
@@ -1970,22 +1976,22 @@
         <v>46307</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F41" s="2">
         <v>9</v>
       </c>
       <c r="G41" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H41" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="356.4">
@@ -1996,22 +2002,22 @@
         <v>46308</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F42" s="2">
         <v>9</v>
       </c>
       <c r="G42" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H42" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="316.8">
@@ -2022,20 +2028,20 @@
         <v>46309</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F43" s="2">
         <v>8</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="409.6">
@@ -2046,37 +2052,49 @@
         <v>46310</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D44" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F44" s="2">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="H44" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F44" s="2">
-        <v>8</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
+    </row>
+    <row r="45" spans="1:8" ht="409.6">
       <c r="A45" s="2">
         <v>40</v>
       </c>
-      <c r="B45" s="3"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="3"/>
+      <c r="B45" s="5">
+        <v>46311</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>145</v>
+      </c>
       <c r="E45" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" s="2"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
+        <v>23</v>
+      </c>
+      <c r="F45" s="2">
+        <v>9</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>147</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/frontend/Frontend-Daily-Tracker.xlsx
+++ b/frontend/Frontend-Daily-Tracker.xlsx
@@ -977,7 +977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2096,12 +2096,48 @@
         <v>147</v>
       </c>
     </row>
+    <row r="46" spans="1:8" ht="409.6">
+      <c r="A46" s="2">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5">
+        <v>46321</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Week 9</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Continued the customer side of the Restaurant SaaS, ready for the Japan launch. The “Cities we deliver to” section was hard coded, so cities now come from the database and admins manage them on a new Cities page, with 16 seeded cities. The home page headline and the map now follow where the visitor is (the nearest city, otherwise the city with the most restaurants), and I fixed the bug where picking Patan from Kathmandu on the map did nothing. Prices now use each restaurant’s own currency, and I added Japanese fonts and fixed the Japanese text spacing. After the supervisor said the home page had too much on it, I made a simpler version on its own branch so we can combine it with Pranav’s: the trending, how-it-works and why LogicBit sections and the “List my kitchen” banner now show only to visitors who are not logged in, and I removed the hero decorations, the red strip, the squiggles and the near-you wording. A restaurant’s badge changes from New to its rating after its first order, the owner banner is dark crimson, and the cuisine cards are crimson shades with faded food photos on one line. I rebuilt the hero with the UI/UX guidelines so text no longer runs over the photo. On the restaurant page, the sections now follow the order, visibility and titles the owner sets in the storefront builder, Special Offers shows the restaurant’s real coupons instead of placeholder offers, and the About and Contact cards were redesigned with a square map. The menu has category chips and a collapsing search under Full menu, matching dish cards and a sticky cart, and broken images from the old database now load. The checkout address map now keeps the pin in the centre while you drag the map. I switched the app to the older database without losing its data, added the footer’s dark-mode brown and fixed the phone layout of the cuisine cards, the contact map and the search box. On the owner side I found there was no error page at all, so I added retry cards, a crash screen and a Page not found screen, then wrote a setup guide, the delivery services code and a patch for the new teammate, and reviewed and merged his branch. I also did a lean code review and applied four clean-ups, checked that the Auto Hub project can be hosted on a VPS, committed, pushed to customer-redesign, opened pull request 34, merged the latest main into it and fixed the two conflicts so it can be merged, then closed the servers.</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Complete</t>
+        </is>
+      </c>
+      <c r="F46" s="2">
+        <v>8</v>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">feat(customer): minimal home, location-driven cities, real storefront offers and menu polish | feat(customer): faded-photo cuisine cards, fixed-pin address map, dark footer and owner error cards</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No blockers. Pushed to customer-redesign and pull request 34 is open and shows no conflicts. After it merges, everyone needs a prisma db push and a re-seed because of the new cities table, and the server also gained cities, offers in the storefront response and real order counts for ranking. Not done yet: the currency change for the owner and admin pages and the currency saved on each order, the retry cards on the remaining owner pages, checking the menu, cart and checkout on a phone, and testing a real courier price in checkout. Decisions waiting on the team: which home page version we keep once we combine mine with Pranav’s, and the backend routes for connecting delivery services.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E5:E45">
+  <conditionalFormatting sqref="E5:E46">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
@@ -2116,7 +2152,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="E5:E45" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="E5:E46" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Todo,In Progress,Blocked,Complete"</formula1>
     </dataValidation>
   </dataValidations>

--- a/frontend/Frontend-Daily-Tracker.xlsx
+++ b/frontend/Frontend-Daily-Tracker.xlsx
@@ -977,7 +977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2132,12 +2132,48 @@
         </is>
       </c>
     </row>
+    <row r="47" spans="1:8" ht="409.6">
+      <c r="A47" s="2">
+        <v>42</v>
+      </c>
+      <c r="B47" s="5">
+        <v>46322</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Day 2</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Continued the customer side of the Restaurant SaaS and checked it against the team's latest changes. I pulled the new seed from main (20 restaurants with 80–120 dishes each) and tested the whole site on it: the home page, restaurant list, a restaurant page, cart, checkout, placing a real order, the owner pages and the admin login. Everything worked. I found two setup traps and wrote them down: a stale cache that makes every page 404 after switching branches, and a port mismatch between the website and the API's allowed origins. I built a customer chatbot with the UI/UX guidelines, with a smooth open and close animation in the site's crimson style. It knows which restaurant the visitor is on and answers about the menu, location, contact, delivery time, offers and opening hours from real data. It has quick-reply chips, bold text and safe links in replies, an end-chat confirmation, a name box for guests, and a saved conversation for each account and restaurant. Everything is in English and Japanese. I compared it with the chatbot I built for the Auto Hub project, listed what a frontend can and can't do without a server, and made a handoff zip for my friend who will build the chatbot backend. The zip has a setup guide PDF, the env files and the Auto Hub chat code as a reference. I found that restaurants only have a manual open/closed switch, so I added real opening hours. The database now stores a weekly schedule and a time zone, one server function decides if a restaurant is open (it handles split shifts, closing after midnight and closed days), and checkout refuses orders while a restaurant is closed. Owners get a weekly editor in Settings. The restaurant's About section shows Open now with the closing time and the full week. The chatbot gives real hours. I tested closing a day as an owner and saw the page, the chatbot and checkout all react. I added pagination to the menu, 10 dishes per page for each category with numbered pages that reset when you search. I also restyled the login, sign-up and for-restaurants panels in crimson with square photos and fixed their spacing, made the restaurant banner shorter, made the favorites cards clickable, changed the empty dish tiles to a soft peach, restyled the footer button, moved the Sponsored tag off the Open badge, and removed the yellow shapes from the Why LogicBit section. I ran a lean code review and applied 8 clean-ups, including deleting a dead duplicate pager. I committed, pushed to customer-redesign, opened pull request 36 and closed the servers.</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Complete</t>
+        </is>
+      </c>
+      <c r="F47" s="2">
+        <v>9</v>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">feat(customer): chatbot widget with restaurant-aware replies, crimson auth panel, softer menu tiles, clickable favorites and footer polish | feat(customer,owner,server): weekly opening hours with open-now status, paginated menu, crimson for-restaurants panel and Sponsored tag fix</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No blockers. Pushed to customer-redesign and pull request 36 is open with no conflicts, and Pranav is asked to review it. After it merges, everyone needs a prisma db push for the two new restaurant columns, and the updated seed gives all 20 restaurants weekly hours. The schema and server changes need Pranav's review. Not done yet: the chatbot backend (saved chats, owner replies, AI answers), which my friend will build from the handoff zip; a friendly closed notice on the cart and checkout pages; and checking the new panels, pagination and opening hours on a phone. Decision waiting on the team: whether the numbered menu pager should be replaced by the simpler shared pager.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E5:E46">
+  <conditionalFormatting sqref="E5:E47">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"Todo"</formula>
     </cfRule>
@@ -2152,7 +2188,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="E5:E46" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="E5:E47" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Todo,In Progress,Blocked,Complete"</formula1>
     </dataValidation>
   </dataValidations>
